--- a/data/KRW-KAITO.xlsx
+++ b/data/KRW-KAITO.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G277"/>
+  <dimension ref="A1:M277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,36 @@
           <t>value</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>BB_Middle</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB_Upper</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>BB_Lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_26_12</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_Signal_26_12_9</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RSI_14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -488,6 +518,12 @@
       <c r="G2" t="n">
         <v>55873132384.25751</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -511,6 +547,12 @@
       <c r="G3" t="n">
         <v>24550910916.25331</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -534,6 +576,12 @@
       <c r="G4" t="n">
         <v>9914378752.642859</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -557,6 +605,12 @@
       <c r="G5" t="n">
         <v>16443897486.11883</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -580,6 +634,12 @@
       <c r="G6" t="n">
         <v>11400770236.64803</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -603,6 +663,12 @@
       <c r="G7" t="n">
         <v>12038662076.04835</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -626,6 +692,12 @@
       <c r="G8" t="n">
         <v>10440554554.93202</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -649,6 +721,12 @@
       <c r="G9" t="n">
         <v>7052532125.452533</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -672,6 +750,12 @@
       <c r="G10" t="n">
         <v>5674944738.717604</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -695,6 +779,12 @@
       <c r="G11" t="n">
         <v>4199179572.559195</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -718,6 +808,12 @@
       <c r="G12" t="n">
         <v>4891924019.79463</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -741,6 +837,12 @@
       <c r="G13" t="n">
         <v>3309088773.666612</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -764,6 +866,12 @@
       <c r="G14" t="n">
         <v>3372996975.91832</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -787,6 +895,14 @@
       <c r="G15" t="n">
         <v>4327529199.882434</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>34.79759232071912</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -810,6 +926,14 @@
       <c r="G16" t="n">
         <v>6115926045.46744</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>33.40188980500447</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -833,6 +957,14 @@
       <c r="G17" t="n">
         <v>2867459071.710691</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>31.62600017888427</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -856,6 +988,14 @@
       <c r="G18" t="n">
         <v>3816714758.544125</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>29.91325300723412</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -879,6 +1019,14 @@
       <c r="G19" t="n">
         <v>1265190544.950625</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>29.45081273349996</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -902,6 +1050,14 @@
       <c r="G20" t="n">
         <v>1280862583.032411</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>34.44040319669331</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -925,6 +1081,20 @@
       <c r="G21" t="n">
         <v>1831548004.168087</v>
       </c>
+      <c r="H21" t="n">
+        <v>3003.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3344.91381695602</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2662.58618304398</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>36.70035975885945</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -948,6 +1118,20 @@
       <c r="G22" t="n">
         <v>1522663173.05347</v>
       </c>
+      <c r="H22" t="n">
+        <v>2979.65</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3276.611462146186</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2682.688537853815</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>32.37378264608866</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -971,6 +1155,20 @@
       <c r="G23" t="n">
         <v>757685895.2662778</v>
       </c>
+      <c r="H23" t="n">
+        <v>2955.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3186.236857418758</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2724.963142581242</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>34.22935709530708</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -994,6 +1192,20 @@
       <c r="G24" t="n">
         <v>1001124838.880157</v>
       </c>
+      <c r="H24" t="n">
+        <v>2932.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3055.644052316493</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2809.755947683506</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>36.4211886012789</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1017,6 +1229,20 @@
       <c r="G25" t="n">
         <v>1765492319.122417</v>
       </c>
+      <c r="H25" t="n">
+        <v>2921.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3019.028267392865</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2824.871732607134</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>33.26594220996704</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1040,6 +1266,20 @@
       <c r="G26" t="n">
         <v>2330453143.52161</v>
       </c>
+      <c r="H26" t="n">
+        <v>2911.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2994.741855550919</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2827.458144449081</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>29.54147387182138</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1063,6 +1303,22 @@
       <c r="G27" t="n">
         <v>1121850946.11664</v>
       </c>
+      <c r="H27" t="n">
+        <v>2904.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2986.290122100785</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2823.309877899216</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-82.95744358947695</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>32.15900194453978</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1086,6 +1342,22 @@
       <c r="G28" t="n">
         <v>1190571468.236008</v>
       </c>
+      <c r="H28" t="n">
+        <v>2904.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2986.396275861609</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2822.603724138391</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-79.35842149377686</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>35.69637321026994</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1109,6 +1381,22 @@
       <c r="G29" t="n">
         <v>998889442.4424155</v>
       </c>
+      <c r="H29" t="n">
+        <v>2902.65</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2985.003567014433</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2820.296432985567</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-75.15567288325656</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>36.66629466327457</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1132,6 +1420,22 @@
       <c r="G30" t="n">
         <v>1235740841.669061</v>
       </c>
+      <c r="H30" t="n">
+        <v>2898.85</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2985.124619674623</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2812.575380325377</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-74.11755732933625</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>33.16463189644719</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1155,6 +1459,22 @@
       <c r="G31" t="n">
         <v>2415816680.601048</v>
       </c>
+      <c r="H31" t="n">
+        <v>2895.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2985.906444213739</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2805.893555786261</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-72.53934648419272</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>33.07740332115561</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1178,6 +1498,22 @@
       <c r="G32" t="n">
         <v>810719807.0239269</v>
       </c>
+      <c r="H32" t="n">
+        <v>2896.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2984.696371807466</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2808.303628192534</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-70.87505768547135</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>32.61548821079046</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1201,6 +1537,22 @@
       <c r="G33" t="n">
         <v>737874561.2209221</v>
       </c>
+      <c r="H33" t="n">
+        <v>2895.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2986.288765824857</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2804.711234175143</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-69.32183930829069</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>31.94294766872461</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1224,6 +1576,22 @@
       <c r="G34" t="n">
         <v>2346060280.800379</v>
       </c>
+      <c r="H34" t="n">
+        <v>2889.35</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2987.914243009322</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2790.785756990677</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-69.46878400641617</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>29.42278394378035</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1247,6 +1615,24 @@
       <c r="G35" t="n">
         <v>3330571416.29344</v>
       </c>
+      <c r="H35" t="n">
+        <v>2877.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2984.009171758606</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2771.390828241394</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-72.86062063308054</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-73.80452709581336</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25.35378429383208</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1270,6 +1656,24 @@
       <c r="G36" t="n">
         <v>2743106259.849683</v>
       </c>
+      <c r="H36" t="n">
+        <v>2865.75</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2984.071384373244</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2747.428615626756</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-76.76179610259669</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-74.39598089717003</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.56461248213489</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1293,6 +1697,24 @@
       <c r="G37" t="n">
         <v>2539687876.718058</v>
       </c>
+      <c r="H37" t="n">
+        <v>2857.05</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2978.678080639304</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2735.421919360697</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-75.83238319577777</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-74.68326135689159</v>
+      </c>
+      <c r="M37" t="n">
+        <v>31.38622848257739</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1316,6 +1738,24 @@
       <c r="G38" t="n">
         <v>2250154144.422458</v>
       </c>
+      <c r="H38" t="n">
+        <v>2851.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2973.140313268422</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2729.259686731578</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-71.7670895144156</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-74.10002698839639</v>
+      </c>
+      <c r="M38" t="n">
+        <v>36.91244018921188</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1339,6 +1779,24 @@
       <c r="G39" t="n">
         <v>1008447467.899585</v>
       </c>
+      <c r="H39" t="n">
+        <v>2845.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2967.964164152251</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2722.435835847748</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-68.56189259010716</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-72.99240010873855</v>
+      </c>
+      <c r="M39" t="n">
+        <v>35.90776069506283</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1362,6 +1820,24 @@
       <c r="G40" t="n">
         <v>1918479707.693145</v>
       </c>
+      <c r="H40" t="n">
+        <v>2837.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2956.152761412749</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2718.047238587251</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-66.06708710707153</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-71.60733750840515</v>
+      </c>
+      <c r="M40" t="n">
+        <v>34.88521924413514</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1385,6 +1861,24 @@
       <c r="G41" t="n">
         <v>829082265.3845695</v>
       </c>
+      <c r="H41" t="n">
+        <v>2827.8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2938.581947987932</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2717.018052012068</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-64.0775148670059</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-70.1013729801253</v>
+      </c>
+      <c r="M41" t="n">
+        <v>33.94822512270541</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1408,6 +1902,24 @@
       <c r="G42" t="n">
         <v>2267608378.887212</v>
       </c>
+      <c r="H42" t="n">
+        <v>2822.95</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2929.605473371041</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2716.294526628958</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-58.99648231576384</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-67.88039484725302</v>
+      </c>
+      <c r="M42" t="n">
+        <v>40.62696981489034</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1431,6 +1943,24 @@
       <c r="G43" t="n">
         <v>1183857801.430358</v>
       </c>
+      <c r="H43" t="n">
+        <v>2817.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2917.08245812643</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2718.717541873571</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-53.7051151338419</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-65.0453389045708</v>
+      </c>
+      <c r="M43" t="n">
+        <v>42.06884984524578</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1454,6 +1984,24 @@
       <c r="G44" t="n">
         <v>2731218399.776114</v>
       </c>
+      <c r="H44" t="n">
+        <v>2813.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2900.004315197813</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2726.195684802186</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-47.43176346556857</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-61.52262381677036</v>
+      </c>
+      <c r="M44" t="n">
+        <v>45.45673986038815</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -1477,6 +2025,24 @@
       <c r="G45" t="n">
         <v>1504484610.396917</v>
       </c>
+      <c r="H45" t="n">
+        <v>2808.75</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2889.083990315438</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2728.416009684562</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-44.20982966888096</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-58.06006498719248</v>
+      </c>
+      <c r="M45" t="n">
+        <v>41.59610334400624</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -1500,6 +2066,24 @@
       <c r="G46" t="n">
         <v>2139165046.390385</v>
       </c>
+      <c r="H46" t="n">
+        <v>2806.65</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2886.217015779159</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2727.082984220841</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-41.58056723935215</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-54.76416543762442</v>
+      </c>
+      <c r="M46" t="n">
+        <v>40.92764546557892</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1523,6 +2107,24 @@
       <c r="G47" t="n">
         <v>4099497911.907325</v>
       </c>
+      <c r="H47" t="n">
+        <v>2805.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2884.012482997283</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2727.787517002717</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-35.61655174910175</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-50.93464269991989</v>
+      </c>
+      <c r="M47" t="n">
+        <v>48.58063687059983</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -1546,6 +2148,24 @@
       <c r="G48" t="n">
         <v>1333779348.523271</v>
       </c>
+      <c r="H48" t="n">
+        <v>2803.55</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2875.944682125146</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2731.155317874855</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-31.33572420831706</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-47.01485900159933</v>
+      </c>
+      <c r="M48" t="n">
+        <v>47.05391837606177</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -1569,6 +2189,24 @@
       <c r="G49" t="n">
         <v>1202301012.944205</v>
       </c>
+      <c r="H49" t="n">
+        <v>2799.85</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2863.241718702058</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2736.458281297942</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-29.2999109019097</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-43.47186938166141</v>
+      </c>
+      <c r="M49" t="n">
+        <v>43.93160284310673</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1592,6 +2230,24 @@
       <c r="G50" t="n">
         <v>704734380.1612025</v>
       </c>
+      <c r="H50" t="n">
+        <v>2798</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2858.577223442486</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2737.422776557514</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-27.53054251766616</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-40.28360400886236</v>
+      </c>
+      <c r="M50" t="n">
+        <v>43.63463615328661</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1615,6 +2271,24 @@
       <c r="G51" t="n">
         <v>901385065.2976915</v>
       </c>
+      <c r="H51" t="n">
+        <v>2795.7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2853.135529073917</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2738.264470926082</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-26.62826765801447</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-37.55253673869279</v>
+      </c>
+      <c r="M51" t="n">
+        <v>42.10217351965228</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1638,6 +2312,24 @@
       <c r="G52" t="n">
         <v>750595483.6690724</v>
       </c>
+      <c r="H52" t="n">
+        <v>2793.3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2847.908058013455</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2738.691941986545</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-26.1763056721561</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-35.27729052538545</v>
+      </c>
+      <c r="M52" t="n">
+        <v>41.01625494418982</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -1661,6 +2353,24 @@
       <c r="G53" t="n">
         <v>670478051.8325323</v>
       </c>
+      <c r="H53" t="n">
+        <v>2791.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2843.639448695415</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2739.160551304586</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-25.28458268412305</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-33.27874895713298</v>
+      </c>
+      <c r="M53" t="n">
+        <v>41.71014966539587</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1684,6 +2394,24 @@
       <c r="G54" t="n">
         <v>1064661545.414868</v>
       </c>
+      <c r="H54" t="n">
+        <v>2791.25</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2843.395469601882</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2739.104530398118</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-23.65961928684192</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-31.35492302307476</v>
+      </c>
+      <c r="M54" t="n">
+        <v>43.61507374768331</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -1707,6 +2435,24 @@
       <c r="G55" t="n">
         <v>1676489082.751039</v>
       </c>
+      <c r="H55" t="n">
+        <v>2791.6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2842.717120419687</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2740.482879580312</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-25.38752979567471</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-30.16144437759475</v>
+      </c>
+      <c r="M55" t="n">
+        <v>36.95035404423118</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -1730,6 +2476,24 @@
       <c r="G56" t="n">
         <v>1664841043.657386</v>
       </c>
+      <c r="H56" t="n">
+        <v>2793.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2836.825338225521</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2749.97466177448</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-26.21267301717398</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-29.3716901055106</v>
+      </c>
+      <c r="M56" t="n">
+        <v>37.70051049344691</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -1753,6 +2517,24 @@
       <c r="G57" t="n">
         <v>1417934329.763556</v>
       </c>
+      <c r="H57" t="n">
+        <v>2793.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2836.653215407439</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2750.346784592561</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-26.16157242983445</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-28.72966657037537</v>
+      </c>
+      <c r="M57" t="n">
+        <v>39.0031082712713</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -1776,6 +2558,24 @@
       <c r="G58" t="n">
         <v>917434630.5479406</v>
       </c>
+      <c r="H58" t="n">
+        <v>2791.35</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2838.306469202878</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2744.393530797122</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-26.94020789639353</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-28.371774835579</v>
+      </c>
+      <c r="M58" t="n">
+        <v>36.68989824022889</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -1799,6 +2599,24 @@
       <c r="G59" t="n">
         <v>1023652986.045607</v>
       </c>
+      <c r="H59" t="n">
+        <v>2790.15</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2838.985540336939</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2741.314459663061</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-26.52529029445077</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-28.00247792735336</v>
+      </c>
+      <c r="M59" t="n">
+        <v>39.18686299502573</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -1822,6 +2640,24 @@
       <c r="G60" t="n">
         <v>570210432.6123098</v>
       </c>
+      <c r="H60" t="n">
+        <v>2790.05</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2839.02540198917</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2741.07459801083</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-24.94066493344826</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-27.39011532857234</v>
+      </c>
+      <c r="M60" t="n">
+        <v>42.44625367160614</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -1845,6 +2681,24 @@
       <c r="G61" t="n">
         <v>896361490.8174534</v>
       </c>
+      <c r="H61" t="n">
+        <v>2789.65</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2839.559017221348</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2739.740982778652</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-24.61150643199608</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-26.83439354925709</v>
+      </c>
+      <c r="M61" t="n">
+        <v>39.58986237844633</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -1868,6 +2722,24 @@
       <c r="G62" t="n">
         <v>707131423.0483276</v>
       </c>
+      <c r="H62" t="n">
+        <v>2787.55</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2839.049417472441</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2736.050582527559</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-23.99337362963888</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-26.26618956533345</v>
+      </c>
+      <c r="M62" t="n">
+        <v>39.88032375608067</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -1891,6 +2763,24 @@
       <c r="G63" t="n">
         <v>1751357397.424068</v>
       </c>
+      <c r="H63" t="n">
+        <v>2783.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2840.690138767512</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2726.109861232489</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-25.86813142118672</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-26.1865779365041</v>
+      </c>
+      <c r="M63" t="n">
+        <v>34.06028967035817</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -1914,6 +2804,24 @@
       <c r="G64" t="n">
         <v>635837667.85403</v>
       </c>
+      <c r="H64" t="n">
+        <v>2778.8</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2836.122246990158</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2721.477753009842</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-26.24444443255652</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-26.19815123571459</v>
+      </c>
+      <c r="M64" t="n">
+        <v>37.05792403668882</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -1937,6 +2845,24 @@
       <c r="G65" t="n">
         <v>2182918329.507989</v>
       </c>
+      <c r="H65" t="n">
+        <v>2773.6</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2840.686213188706</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2706.513786811293</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-29.43107776701936</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-26.84473654197555</v>
+      </c>
+      <c r="M65" t="n">
+        <v>30.9893253311849</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -1960,6 +2886,24 @@
       <c r="G66" t="n">
         <v>2376218515.490029</v>
       </c>
+      <c r="H66" t="n">
+        <v>2768.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2844.756200793412</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2691.543799206589</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-32.39005171547888</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-27.95379957667621</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29.68072642960151</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -1983,6 +2927,24 @@
       <c r="G67" t="n">
         <v>1130194140.207856</v>
       </c>
+      <c r="H67" t="n">
+        <v>2761.35</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2836.432021816147</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2686.267978183853</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-33.0628654732127</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-28.97561275598351</v>
+      </c>
+      <c r="M67" t="n">
+        <v>34.45020021042338</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2006,6 +2968,24 @@
       <c r="G68" t="n">
         <v>889692959.3075057</v>
       </c>
+      <c r="H68" t="n">
+        <v>2756.1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2826.631978562921</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2685.568021437079</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-31.53800029225522</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-29.48809026323785</v>
+      </c>
+      <c r="M68" t="n">
+        <v>40.1846618001064</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -2029,6 +3009,24 @@
       <c r="G69" t="n">
         <v>774071510.8235786</v>
       </c>
+      <c r="H69" t="n">
+        <v>2751.25</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2820.721936780259</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2681.778063219741</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-31.02093497620854</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-29.79465920583199</v>
+      </c>
+      <c r="M69" t="n">
+        <v>37.97017730142552</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -2052,6 +3050,24 @@
       <c r="G70" t="n">
         <v>433376416.9367565</v>
       </c>
+      <c r="H70" t="n">
+        <v>2746.6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2813.736875113459</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2679.463124886541</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-30.10276773456235</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-29.85628091157806</v>
+      </c>
+      <c r="M70" t="n">
+        <v>38.53140223822668</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -2075,6 +3091,24 @@
       <c r="G71" t="n">
         <v>640107811.2720407</v>
       </c>
+      <c r="H71" t="n">
+        <v>2743.1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2807.218328112951</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2678.981671887048</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-28.00331741436003</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-29.48568821213446</v>
+      </c>
+      <c r="M71" t="n">
+        <v>42.19255804710455</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -2098,6 +3132,24 @@
       <c r="G72" t="n">
         <v>1065389503.620334</v>
       </c>
+      <c r="H72" t="n">
+        <v>2740.05</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2801.26266208882</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2678.83733791118</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-25.87977864594768</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-28.7645062988971</v>
+      </c>
+      <c r="M72" t="n">
+        <v>42.75743688376321</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -2121,6 +3173,24 @@
       <c r="G73" t="n">
         <v>1283219729.949979</v>
       </c>
+      <c r="H73" t="n">
+        <v>2735.35</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2794.912656085839</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2675.78734391416</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-26.31427358641076</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-28.27445975639984</v>
+      </c>
+      <c r="M73" t="n">
+        <v>36.92827036777854</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -2144,6 +3214,24 @@
       <c r="G74" t="n">
         <v>797266361.4444287</v>
       </c>
+      <c r="H74" t="n">
+        <v>2730.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2784.28202678737</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2676.917973212629</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-25.79640753023341</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-27.77884931116655</v>
+      </c>
+      <c r="M74" t="n">
+        <v>39.0173851835096</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -2167,6 +3255,24 @@
       <c r="G75" t="n">
         <v>1810213197.567438</v>
       </c>
+      <c r="H75" t="n">
+        <v>2729.35</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2781.66166217967</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2677.03833782033</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-22.78330554855393</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-26.77974055864403</v>
+      </c>
+      <c r="M75" t="n">
+        <v>46.86901911426947</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -2190,6 +3296,24 @@
       <c r="G76" t="n">
         <v>490849552.7034781</v>
       </c>
+      <c r="H76" t="n">
+        <v>2727.15</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2777.794940517291</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2676.505059482709</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-21.43932757944822</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-25.71165796280487</v>
+      </c>
+      <c r="M76" t="n">
+        <v>43.53834183831236</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -2213,6 +3337,24 @@
       <c r="G77" t="n">
         <v>480979696.3268324</v>
       </c>
+      <c r="H77" t="n">
+        <v>2725.05</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2772.633505545513</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2677.466494454487</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-19.58362600730607</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-24.48605157170511</v>
+      </c>
+      <c r="M77" t="n">
+        <v>45.36753767839414</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -2236,6 +3378,24 @@
       <c r="G78" t="n">
         <v>498436027.6655776</v>
       </c>
+      <c r="H78" t="n">
+        <v>2723.6</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2769.675590066757</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2677.524409933243</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-17.98632561879231</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-23.18610638112255</v>
+      </c>
+      <c r="M78" t="n">
+        <v>45.14253939444071</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -2259,6 +3419,24 @@
       <c r="G79" t="n">
         <v>508772874.2334391</v>
       </c>
+      <c r="H79" t="n">
+        <v>2721.35</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2764.390794602328</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2678.309205397672</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-17.08831163213563</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-21.96654743132517</v>
+      </c>
+      <c r="M79" t="n">
+        <v>43.51563495058591</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -2282,6 +3460,24 @@
       <c r="G80" t="n">
         <v>750946871.4317952</v>
       </c>
+      <c r="H80" t="n">
+        <v>2719.45</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2756.287345181212</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2682.612654818787</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-14.67433131059943</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-20.50810420718003</v>
+      </c>
+      <c r="M80" t="n">
+        <v>48.89890885551169</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -2305,6 +3501,24 @@
       <c r="G81" t="n">
         <v>1320174318.408504</v>
       </c>
+      <c r="H81" t="n">
+        <v>2718.75</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2753.158574512755</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2684.341425487245</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-11.89785862209601</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-18.78605509016322</v>
+      </c>
+      <c r="M81" t="n">
+        <v>51.26812633434837</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -2328,6 +3542,24 @@
       <c r="G82" t="n">
         <v>1647493171.515397</v>
       </c>
+      <c r="H82" t="n">
+        <v>2718.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2752.342554734338</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2684.857445265662</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-8.629706417460966</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-16.75478535562277</v>
+      </c>
+      <c r="M82" t="n">
+        <v>54.30985657632512</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -2351,6 +3583,24 @@
       <c r="G83" t="n">
         <v>845010857.5030354</v>
       </c>
+      <c r="H83" t="n">
+        <v>2718.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2752.969928089149</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2684.830071910851</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-7.885373990268818</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-14.98090308255198</v>
+      </c>
+      <c r="M83" t="n">
+        <v>47.87379590993178</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -2374,6 +3624,24 @@
       <c r="G84" t="n">
         <v>513916394.9545933</v>
       </c>
+      <c r="H84" t="n">
+        <v>2719</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2753.269519984963</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2684.730480015037</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-6.733713268220981</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-13.33146511968578</v>
+      </c>
+      <c r="M84" t="n">
+        <v>49.48548890842908</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -2397,6 +3665,24 @@
       <c r="G85" t="n">
         <v>771332595.1496513</v>
       </c>
+      <c r="H85" t="n">
+        <v>2720.35</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2752.810899556232</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2687.889100443767</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-6.951258705154487</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-12.05542383677952</v>
+      </c>
+      <c r="M85" t="n">
+        <v>45.6826963065087</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -2420,6 +3706,24 @@
       <c r="G86" t="n">
         <v>770781707.6919979</v>
       </c>
+      <c r="H86" t="n">
+        <v>2721.7</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2750.168227904101</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2693.231772095899</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-7.840204461097983</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-11.21237996164322</v>
+      </c>
+      <c r="M86" t="n">
+        <v>43.29407832267771</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -2443,6 +3747,24 @@
       <c r="G87" t="n">
         <v>495013751.2516391</v>
       </c>
+      <c r="H87" t="n">
+        <v>2722.15</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2749.560034658859</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2694.739965341141</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-8.60686903386204</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-10.69127777608698</v>
+      </c>
+      <c r="M87" t="n">
+        <v>42.81193681296691</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -2466,6 +3788,24 @@
       <c r="G88" t="n">
         <v>443266758.2681167</v>
       </c>
+      <c r="H88" t="n">
+        <v>2721.35</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2749.650353354682</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2693.049646645318</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-9.428536502165571</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-10.4387295213027</v>
+      </c>
+      <c r="M88" t="n">
+        <v>41.80909717035176</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -2489,6 +3829,24 @@
       <c r="G89" t="n">
         <v>291138886.8540563</v>
       </c>
+      <c r="H89" t="n">
+        <v>2721.4</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2749.616307341675</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2693.183692658326</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-9.645757037136718</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-10.2801350244695</v>
+      </c>
+      <c r="M89" t="n">
+        <v>43.24091152884113</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -2512,6 +3870,24 @@
       <c r="G90" t="n">
         <v>655535833.1225395</v>
       </c>
+      <c r="H90" t="n">
+        <v>2722.25</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2750.184745389923</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2694.315254610077</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-8.270123472944306</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-9.878132714164463</v>
+      </c>
+      <c r="M90" t="n">
+        <v>49.28791579517322</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -2535,6 +3911,24 @@
       <c r="G91" t="n">
         <v>968319401.7385731</v>
       </c>
+      <c r="H91" t="n">
+        <v>2723.55</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2753.996510473285</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2693.103489526715</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-5.343115712134022</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-8.971129313758375</v>
+      </c>
+      <c r="M91" t="n">
+        <v>55.52467343214796</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -2558,6 +3952,24 @@
       <c r="G92" t="n">
         <v>659679581.3038428</v>
       </c>
+      <c r="H92" t="n">
+        <v>2724.6</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2756.714794098668</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2692.485205901331</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-3.228302045263263</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-7.822563860059353</v>
+      </c>
+      <c r="M92" t="n">
+        <v>54.53965790957562</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -2581,6 +3993,24 @@
       <c r="G93" t="n">
         <v>678590540.7197498</v>
       </c>
+      <c r="H93" t="n">
+        <v>2727.45</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2759.018813724939</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2695.881186275061</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-1.055974505176891</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-6.469245989082862</v>
+      </c>
+      <c r="M93" t="n">
+        <v>56.21274838682636</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -2604,6 +4034,24 @@
       <c r="G94" t="n">
         <v>2392486347.07404</v>
       </c>
+      <c r="H94" t="n">
+        <v>2731.7</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2770.917853077392</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2692.482146922608</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3.450048205776511</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-4.485387150110988</v>
+      </c>
+      <c r="M94" t="n">
+        <v>64.43531148086998</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -2627,6 +4075,24 @@
       <c r="G95" t="n">
         <v>1938879573.573913</v>
       </c>
+      <c r="H95" t="n">
+        <v>2733.15</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2774.396939280387</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2691.903060719613</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4.787244937084324</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-2.630860732671926</v>
+      </c>
+      <c r="M95" t="n">
+        <v>55.73962325816075</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -2650,6 +4116,24 @@
       <c r="G96" t="n">
         <v>756319595.2732565</v>
       </c>
+      <c r="H96" t="n">
+        <v>2735.9</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2779.474763338428</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2692.325236661572</v>
+      </c>
+      <c r="K96" t="n">
+        <v>6.57807149366954</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-0.7890742874036325</v>
+      </c>
+      <c r="M96" t="n">
+        <v>58.00034282143795</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -2673,6 +4157,24 @@
       <c r="G97" t="n">
         <v>941767773.756976</v>
       </c>
+      <c r="H97" t="n">
+        <v>2738.65</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2785.444337264246</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2691.855662735754</v>
+      </c>
+      <c r="K97" t="n">
+        <v>8.464581513857866</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1.061656872848667</v>
+      </c>
+      <c r="M97" t="n">
+        <v>59.55756854000047</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -2696,6 +4198,24 @@
       <c r="G98" t="n">
         <v>1735366308.71821</v>
       </c>
+      <c r="H98" t="n">
+        <v>2742.65</v>
+      </c>
+      <c r="I98" t="n">
+        <v>2796.24953358006</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2689.05046641994</v>
+      </c>
+      <c r="K98" t="n">
+        <v>11.76068387709574</v>
+      </c>
+      <c r="L98" t="n">
+        <v>3.201462273698083</v>
+      </c>
+      <c r="M98" t="n">
+        <v>64.42745311499606</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -2719,6 +4239,24 @@
       <c r="G99" t="n">
         <v>1610039415.097946</v>
       </c>
+      <c r="H99" t="n">
+        <v>2748.05</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2810.456650286649</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2685.643349713351</v>
+      </c>
+      <c r="K99" t="n">
+        <v>15.88428904627517</v>
+      </c>
+      <c r="L99" t="n">
+        <v>5.738027628213501</v>
+      </c>
+      <c r="M99" t="n">
+        <v>68.05248048618446</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -2742,6 +4280,24 @@
       <c r="G100" t="n">
         <v>1046179252.004382</v>
       </c>
+      <c r="H100" t="n">
+        <v>2751.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2817.11823455548</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2685.481765444521</v>
+      </c>
+      <c r="K100" t="n">
+        <v>17.01948638342401</v>
+      </c>
+      <c r="L100" t="n">
+        <v>7.994319379255603</v>
+      </c>
+      <c r="M100" t="n">
+        <v>60.46842321346142</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -2765,6 +4321,24 @@
       <c r="G101" t="n">
         <v>1479531903.957952</v>
       </c>
+      <c r="H101" t="n">
+        <v>2752.1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2817.884192630146</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2686.315807369854</v>
+      </c>
+      <c r="K101" t="n">
+        <v>14.52404855488294</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9.300265214381071</v>
+      </c>
+      <c r="M101" t="n">
+        <v>50.38917142483567</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -2788,6 +4362,24 @@
       <c r="G102" t="n">
         <v>886652123.7066915</v>
       </c>
+      <c r="H102" t="n">
+        <v>2751.55</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2817.411900974692</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2685.688099025308</v>
+      </c>
+      <c r="K102" t="n">
+        <v>11.20683602762347</v>
+      </c>
+      <c r="L102" t="n">
+        <v>9.68157937702955</v>
+      </c>
+      <c r="M102" t="n">
+        <v>47.21112696207952</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -2811,6 +4403,24 @@
       <c r="G103" t="n">
         <v>519949702.4344633</v>
       </c>
+      <c r="H103" t="n">
+        <v>2753.35</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2818.833662084524</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2687.866337915475</v>
+      </c>
+      <c r="K103" t="n">
+        <v>10.31492494754639</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9.808248491132918</v>
+      </c>
+      <c r="M103" t="n">
+        <v>52.19032919320824</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -2834,6 +4444,24 @@
       <c r="G104" t="n">
         <v>1603771037.867197</v>
       </c>
+      <c r="H104" t="n">
+        <v>2752.9</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2818.948164243983</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2686.851835756017</v>
+      </c>
+      <c r="K104" t="n">
+        <v>6.387474101930366</v>
+      </c>
+      <c r="L104" t="n">
+        <v>9.124093613292407</v>
+      </c>
+      <c r="M104" t="n">
+        <v>44.52180800530729</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -2857,6 +4485,24 @@
       <c r="G105" t="n">
         <v>609299952.1202511</v>
       </c>
+      <c r="H105" t="n">
+        <v>2753.1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2818.79596639064</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2687.404033609359</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3.078075586396608</v>
+      </c>
+      <c r="L105" t="n">
+        <v>7.914890007913248</v>
+      </c>
+      <c r="M105" t="n">
+        <v>44.16343564327639</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -2880,6 +4526,24 @@
       <c r="G106" t="n">
         <v>327714067.6221749</v>
       </c>
+      <c r="H106" t="n">
+        <v>2754.05</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2817.863713259771</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2690.23628674023</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.849024606005969</v>
+      </c>
+      <c r="L106" t="n">
+        <v>6.501716927531792</v>
+      </c>
+      <c r="M106" t="n">
+        <v>45.34782329959287</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -2903,6 +4567,24 @@
       <c r="G107" t="n">
         <v>477155909.874652</v>
       </c>
+      <c r="H107" t="n">
+        <v>2755.05</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2816.659982957312</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2693.440017042689</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-0.9868304311207794</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5.004007455801278</v>
+      </c>
+      <c r="M107" t="n">
+        <v>45.1415862536827</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -2926,6 +4608,24 @@
       <c r="G108" t="n">
         <v>375263782.9042307</v>
       </c>
+      <c r="H108" t="n">
+        <v>2756.15</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2814.938689388353</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2697.361310611647</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-2.573476623387251</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3.488510639963573</v>
+      </c>
+      <c r="M108" t="n">
+        <v>44.7036929398627</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -2949,6 +4649,24 @@
       <c r="G109" t="n">
         <v>610991983.7317588</v>
       </c>
+      <c r="H109" t="n">
+        <v>2757.35</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2813.229423762242</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2701.470576237758</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-3.30861564441193</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2.129085383088472</v>
+      </c>
+      <c r="M109" t="n">
+        <v>46.38401198422198</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -2972,6 +4690,24 @@
       <c r="G110" t="n">
         <v>168374296.7188934</v>
       </c>
+      <c r="H110" t="n">
+        <v>2757.95</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2812.804261457067</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2703.095738542933</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-3.368241764651884</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1.029619953540401</v>
+      </c>
+      <c r="M110" t="n">
+        <v>48.08299840297818</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -2995,6 +4731,24 @@
       <c r="G111" t="n">
         <v>2020589617.598008</v>
       </c>
+      <c r="H111" t="n">
+        <v>2753.2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2824.093159049376</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2682.306840950624</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-10.15719964501432</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-1.207743966170542</v>
+      </c>
+      <c r="M111" t="n">
+        <v>32.41304306233613</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -3018,6 +4772,24 @@
       <c r="G112" t="n">
         <v>1806753928.692063</v>
       </c>
+      <c r="H112" t="n">
+        <v>2746.95</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2838.079523207356</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2655.820476792644</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-17.99291080888815</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-4.564777334714066</v>
+      </c>
+      <c r="M112" t="n">
+        <v>28.5261776980032</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -3041,6 +4813,24 @@
       <c r="G113" t="n">
         <v>853238234.5604447</v>
       </c>
+      <c r="H113" t="n">
+        <v>2740.55</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2845.943500748386</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2635.156499251615</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-23.68763709615223</v>
+      </c>
+      <c r="L113" t="n">
+        <v>-8.389349287001698</v>
+      </c>
+      <c r="M113" t="n">
+        <v>29.35555039716515</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -3064,6 +4854,24 @@
       <c r="G114" t="n">
         <v>1556536832.772585</v>
       </c>
+      <c r="H114" t="n">
+        <v>2730.9</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2851.407095226795</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2610.392904773205</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-30.27253504661667</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-12.76598643892469</v>
+      </c>
+      <c r="M114" t="n">
+        <v>26.09464096820935</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -3087,6 +4895,24 @@
       <c r="G115" t="n">
         <v>1200799356.578527</v>
       </c>
+      <c r="H115" t="n">
+        <v>2723.65</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2853.152548237475</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2594.147451762525</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-33.41144329787403</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-16.89507781071456</v>
+      </c>
+      <c r="M115" t="n">
+        <v>31.8052469199135</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -3110,6 +4936,24 @@
       <c r="G116" t="n">
         <v>678770107.8047912</v>
       </c>
+      <c r="H116" t="n">
+        <v>2716.4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>2850.636209720029</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2582.163790279972</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-34.69222391298581</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-20.45450703116881</v>
+      </c>
+      <c r="M116" t="n">
+        <v>34.40448348160061</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -3133,6 +4977,24 @@
       <c r="G117" t="n">
         <v>430199931.266969</v>
       </c>
+      <c r="H117" t="n">
+        <v>2709</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2845.141103271567</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2572.858896728433</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-34.98124321071737</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-23.35985426707852</v>
+      </c>
+      <c r="M117" t="n">
+        <v>35.46408120913479</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -3156,6 +5018,24 @@
       <c r="G118" t="n">
         <v>421985499.4008822</v>
       </c>
+      <c r="H118" t="n">
+        <v>2700.7</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2833.345542706867</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2568.054457293133</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-34.33040370653862</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-25.55396415497054</v>
+      </c>
+      <c r="M118" t="n">
+        <v>37.10526454725665</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -3179,6 +5059,24 @@
       <c r="G119" t="n">
         <v>574742985.0461239</v>
       </c>
+      <c r="H119" t="n">
+        <v>2690.55</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2815.024053521202</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2566.075946478798</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-34.70561032056912</v>
+      </c>
+      <c r="L119" t="n">
+        <v>-27.38429338809026</v>
+      </c>
+      <c r="M119" t="n">
+        <v>34.57985300955063</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -3202,6 +5100,24 @@
       <c r="G120" t="n">
         <v>317885752.3656505</v>
       </c>
+      <c r="H120" t="n">
+        <v>2682.3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2798.527535463843</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2566.072464536157</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-33.48726096893461</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-28.60488690425913</v>
+      </c>
+      <c r="M120" t="n">
+        <v>38.52265074067645</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -3225,6 +5141,24 @@
       <c r="G121" t="n">
         <v>408270173.4574716</v>
       </c>
+      <c r="H121" t="n">
+        <v>2674.9</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2789.486037543842</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2560.313962456158</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-33.98585038324973</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-29.68107960005725</v>
+      </c>
+      <c r="M121" t="n">
+        <v>34.81079253979087</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -3248,6 +5182,24 @@
       <c r="G122" t="n">
         <v>531941500.9295054</v>
       </c>
+      <c r="H122" t="n">
+        <v>2667.5</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2782.395604789733</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2552.604395210267</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-35.18576117357361</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-30.78201591476052</v>
+      </c>
+      <c r="M122" t="n">
+        <v>32.60432028409521</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -3271,6 +5223,24 @@
       <c r="G123" t="n">
         <v>380784157.9934748</v>
       </c>
+      <c r="H123" t="n">
+        <v>2659.8</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2767.400371746563</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2552.199628253438</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-34.36875952868695</v>
+      </c>
+      <c r="L123" t="n">
+        <v>-31.49936463754581</v>
+      </c>
+      <c r="M123" t="n">
+        <v>37.44378542884211</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -3294,6 +5264,24 @@
       <c r="G124" t="n">
         <v>190218720.4829591</v>
       </c>
+      <c r="H124" t="n">
+        <v>2653.75</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2758.910591477978</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2548.589408522022</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-33.81562422823527</v>
+      </c>
+      <c r="L124" t="n">
+        <v>-31.9626165556837</v>
+      </c>
+      <c r="M124" t="n">
+        <v>36.44898099515743</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -3317,6 +5305,24 @@
       <c r="G125" t="n">
         <v>365557735.8814372</v>
       </c>
+      <c r="H125" t="n">
+        <v>2647.9</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2749.282246966608</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2546.517753033393</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-32.83734871673323</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-32.13756298789361</v>
+      </c>
+      <c r="M125" t="n">
+        <v>37.04935458577125</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -3340,6 +5346,24 @@
       <c r="G126" t="n">
         <v>421865174.3707868</v>
       </c>
+      <c r="H126" t="n">
+        <v>2642.25</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2736.845718719179</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2547.654281280821</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-30.97873002576443</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-31.90579639546778</v>
+      </c>
+      <c r="M126" t="n">
+        <v>39.80520231664531</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -3363,6 +5387,24 @@
       <c r="G127" t="n">
         <v>233379871.4604706</v>
       </c>
+      <c r="H127" t="n">
+        <v>2635.55</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2723.051942835562</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2548.048057164438</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-30.92449908525305</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-31.70953693342483</v>
+      </c>
+      <c r="M127" t="n">
+        <v>35.69190914855449</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -3386,6 +5428,24 @@
       <c r="G128" t="n">
         <v>133576548.4362868</v>
       </c>
+      <c r="H128" t="n">
+        <v>2629.6</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2706.713941670737</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2552.486058329263</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-29.49255747561892</v>
+      </c>
+      <c r="L128" t="n">
+        <v>-31.26614104186365</v>
+      </c>
+      <c r="M128" t="n">
+        <v>39.65981896005502</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -3409,6 +5469,24 @@
       <c r="G129" t="n">
         <v>123252624.4610379</v>
       </c>
+      <c r="H129" t="n">
+        <v>2623.8</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2684.289999173399</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2563.310000826601</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-27.31661966208094</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-30.47623676590711</v>
+      </c>
+      <c r="M129" t="n">
+        <v>42.31353203891089</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -3432,6 +5510,24 @@
       <c r="G130" t="n">
         <v>118684209.1273738</v>
       </c>
+      <c r="H130" t="n">
+        <v>2617.95</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2646.616879844128</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2589.283120155872</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-24.90166417099454</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-29.3613222469246</v>
+      </c>
+      <c r="M130" t="n">
+        <v>43.7924835336743</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -3455,6 +5551,24 @@
       <c r="G131" t="n">
         <v>163549269.7720649</v>
       </c>
+      <c r="H131" t="n">
+        <v>2616.95</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2641.473254270134</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2592.426745729865</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-21.76856041961946</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-27.84276988146357</v>
+      </c>
+      <c r="M131" t="n">
+        <v>47.28554047417993</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -3478,6 +5592,24 @@
       <c r="G132" t="n">
         <v>720727815.7013029</v>
       </c>
+      <c r="H132" t="n">
+        <v>2618.55</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2647.885814288984</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2589.214185711017</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-17.55010522501334</v>
+      </c>
+      <c r="L132" t="n">
+        <v>-25.78423695017353</v>
+      </c>
+      <c r="M132" t="n">
+        <v>52.3362933525085</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -3501,6 +5633,24 @@
       <c r="G133" t="n">
         <v>441616093.4479573</v>
       </c>
+      <c r="H133" t="n">
+        <v>2621.25</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2660.670172500862</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2581.829827499138</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-12.0507445429148</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-23.03753846872178</v>
+      </c>
+      <c r="M133" t="n">
+        <v>58.03394159659751</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -3524,6 +5674,24 @@
       <c r="G134" t="n">
         <v>1051091897.194283</v>
       </c>
+      <c r="H134" t="n">
+        <v>2627.2</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2681.926958621851</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2572.473041378149</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-4.812775409727237</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-19.39258585692287</v>
+      </c>
+      <c r="M134" t="n">
+        <v>64.44239262543778</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -3547,6 +5715,24 @@
       <c r="G135" t="n">
         <v>213301198.8861435</v>
       </c>
+      <c r="H135" t="n">
+        <v>2631.65</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2695.691470938743</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2567.608529061257</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.1948958531374956</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-15.4750895149108</v>
+      </c>
+      <c r="M135" t="n">
+        <v>61.82783581593808</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -3570,6 +5756,24 @@
       <c r="G136" t="n">
         <v>488932184.7638244</v>
       </c>
+      <c r="H136" t="n">
+        <v>2634.2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2701.134594941614</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2567.265405058386</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1.882445750218267</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-12.00358246188499</v>
+      </c>
+      <c r="M136" t="n">
+        <v>54.42909603803639</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -3593,6 +5797,24 @@
       <c r="G137" t="n">
         <v>347022916.1952515</v>
       </c>
+      <c r="H137" t="n">
+        <v>2636.2</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2704.880710537952</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2567.519289462048</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2.62474329636143</v>
+      </c>
+      <c r="L137" t="n">
+        <v>-9.077917310235705</v>
+      </c>
+      <c r="M137" t="n">
+        <v>52.73023405040978</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -3616,6 +5838,24 @@
       <c r="G138" t="n">
         <v>186321113.2067716</v>
       </c>
+      <c r="H138" t="n">
+        <v>2637.8</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2707.864541674074</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2567.735458325927</v>
+      </c>
+      <c r="K138" t="n">
+        <v>3.016859683837083</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-6.658961911421148</v>
+      </c>
+      <c r="M138" t="n">
+        <v>52.22864004899181</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -3639,6 +5879,24 @@
       <c r="G139" t="n">
         <v>286638386.9902591</v>
       </c>
+      <c r="H139" t="n">
+        <v>2640.4</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2711.481361832748</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2569.318638167252</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3.608781529479074</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-4.605413223241104</v>
+      </c>
+      <c r="M139" t="n">
+        <v>53.18774660867869</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -3662,6 +5920,24 @@
       <c r="G140" t="n">
         <v>164869572.330891</v>
       </c>
+      <c r="H140" t="n">
+        <v>2642.55</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2715.308435936997</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2569.791564063003</v>
+      </c>
+      <c r="K140" t="n">
+        <v>4.430272644674915</v>
+      </c>
+      <c r="L140" t="n">
+        <v>-2.7982760496579</v>
+      </c>
+      <c r="M140" t="n">
+        <v>54.41963607356201</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -3685,6 +5961,24 @@
       <c r="G141" t="n">
         <v>245092729.7208971</v>
       </c>
+      <c r="H141" t="n">
+        <v>2645</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2716.635186884646</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2573.364813115354</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3.667278246099613</v>
+      </c>
+      <c r="L141" t="n">
+        <v>-1.505165190506398</v>
+      </c>
+      <c r="M141" t="n">
+        <v>49.63685952889323</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -3708,6 +6002,24 @@
       <c r="G142" t="n">
         <v>145581146.6921935</v>
       </c>
+      <c r="H142" t="n">
+        <v>2647.35</v>
+      </c>
+      <c r="I142" t="n">
+        <v>2715.394911639286</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2579.305088360714</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.671572911077874</v>
+      </c>
+      <c r="L142" t="n">
+        <v>-0.8698175701895434</v>
+      </c>
+      <c r="M142" t="n">
+        <v>45.34506276161708</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -3731,6 +6043,24 @@
       <c r="G143" t="n">
         <v>93783937.89932372</v>
       </c>
+      <c r="H143" t="n">
+        <v>2648.85</v>
+      </c>
+      <c r="I143" t="n">
+        <v>2715.098849046592</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2582.601150953407</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.08893684619124542</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-0.6780666869133857</v>
+      </c>
+      <c r="M143" t="n">
+        <v>45.34506276161709</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -3754,6 +6084,24 @@
       <c r="G144" t="n">
         <v>235708201.3146477</v>
       </c>
+      <c r="H144" t="n">
+        <v>2651.05</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2714.454968259579</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2587.645031740421</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-0.5138570718390838</v>
+      </c>
+      <c r="L144" t="n">
+        <v>-0.6452247638985253</v>
+      </c>
+      <c r="M144" t="n">
+        <v>47.80797768023035</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -3777,6 +6125,24 @@
       <c r="G145" t="n">
         <v>125030156.6919097</v>
       </c>
+      <c r="H145" t="n">
+        <v>2652.4</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2713.265096730378</v>
+      </c>
+      <c r="J145" t="n">
+        <v>2591.534903269622</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-2.176856784577012</v>
+      </c>
+      <c r="L145" t="n">
+        <v>-0.9515511680342228</v>
+      </c>
+      <c r="M145" t="n">
+        <v>43.82062599475891</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -3800,6 +6166,24 @@
       <c r="G146" t="n">
         <v>292780737.2310452</v>
       </c>
+      <c r="H146" t="n">
+        <v>2652.15</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2713.616332247811</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2590.68366775219</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-5.289727137467708</v>
+      </c>
+      <c r="L146" t="n">
+        <v>-1.81918636192092</v>
+      </c>
+      <c r="M146" t="n">
+        <v>38.51608762050723</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -3823,6 +6207,24 @@
       <c r="G147" t="n">
         <v>123858398.9710782</v>
       </c>
+      <c r="H147" t="n">
+        <v>2653.8</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2710.754718856283</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2596.845281143717</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-6.391950608963725</v>
+      </c>
+      <c r="L147" t="n">
+        <v>-2.733739211329481</v>
+      </c>
+      <c r="M147" t="n">
+        <v>43.62827941411687</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -3846,6 +6248,24 @@
       <c r="G148" t="n">
         <v>69948330.4160324</v>
       </c>
+      <c r="H148" t="n">
+        <v>2655.25</v>
+      </c>
+      <c r="I148" t="n">
+        <v>2708.95242080203</v>
+      </c>
+      <c r="J148" t="n">
+        <v>2601.54757919797</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-6.46472454692821</v>
+      </c>
+      <c r="L148" t="n">
+        <v>-3.479936278449227</v>
+      </c>
+      <c r="M148" t="n">
+        <v>46.3314456311425</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -3869,6 +6289,24 @@
       <c r="G149" t="n">
         <v>134169605.0444676</v>
       </c>
+      <c r="H149" t="n">
+        <v>2656.25</v>
+      </c>
+      <c r="I149" t="n">
+        <v>2707.844088808683</v>
+      </c>
+      <c r="J149" t="n">
+        <v>2604.655911191317</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-6.448069090382432</v>
+      </c>
+      <c r="L149" t="n">
+        <v>-4.073562840835868</v>
+      </c>
+      <c r="M149" t="n">
+        <v>46.3314456311425</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -3892,6 +6330,24 @@
       <c r="G150" t="n">
         <v>60125508.36129491</v>
       </c>
+      <c r="H150" t="n">
+        <v>2657.1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>2707.00751446424</v>
+      </c>
+      <c r="J150" t="n">
+        <v>2607.19248553576</v>
+      </c>
+      <c r="K150" t="n">
+        <v>-6.201993515135655</v>
+      </c>
+      <c r="L150" t="n">
+        <v>-4.499248975695826</v>
+      </c>
+      <c r="M150" t="n">
+        <v>46.98661539410552</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -3915,6 +6371,24 @@
       <c r="G151" t="n">
         <v>173453887.4436068</v>
       </c>
+      <c r="H151" t="n">
+        <v>2656.85</v>
+      </c>
+      <c r="I151" t="n">
+        <v>2707.245535516535</v>
+      </c>
+      <c r="J151" t="n">
+        <v>2606.454464483465</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-6.736242069969194</v>
+      </c>
+      <c r="L151" t="n">
+        <v>-4.9466475945505</v>
+      </c>
+      <c r="M151" t="n">
+        <v>44.08851073243797</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -3938,6 +6412,24 @@
       <c r="G152" t="n">
         <v>39754203.69673136</v>
       </c>
+      <c r="H152" t="n">
+        <v>2655.2</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2707.965898078193</v>
+      </c>
+      <c r="J152" t="n">
+        <v>2602.434101921806</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-7.795995301592029</v>
+      </c>
+      <c r="L152" t="n">
+        <v>-5.516517135958805</v>
+      </c>
+      <c r="M152" t="n">
+        <v>41.60150850295548</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -3961,6 +6453,24 @@
       <c r="G153" t="n">
         <v>87234953.2782516</v>
       </c>
+      <c r="H153" t="n">
+        <v>2652.85</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2705.352476132067</v>
+      </c>
+      <c r="J153" t="n">
+        <v>2600.347523867933</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-7.659950166234921</v>
+      </c>
+      <c r="L153" t="n">
+        <v>-5.945203742014029</v>
+      </c>
+      <c r="M153" t="n">
+        <v>45.63780091401684</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -3984,6 +6494,24 @@
       <c r="G154" t="n">
         <v>56993580.55260165</v>
       </c>
+      <c r="H154" t="n">
+        <v>2648.8</v>
+      </c>
+      <c r="I154" t="n">
+        <v>2693.764875180503</v>
+      </c>
+      <c r="J154" t="n">
+        <v>2603.835124819498</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-7.386297138064037</v>
+      </c>
+      <c r="L154" t="n">
+        <v>-6.233422421224031</v>
+      </c>
+      <c r="M154" t="n">
+        <v>46.00317790213883</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -4007,6 +6535,24 @@
       <c r="G155" t="n">
         <v>51883116.44264706</v>
       </c>
+      <c r="H155" t="n">
+        <v>2645.2</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2682.459092849909</v>
+      </c>
+      <c r="J155" t="n">
+        <v>2607.940907150091</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-7.087722291057162</v>
+      </c>
+      <c r="L155" t="n">
+        <v>-6.404282395190657</v>
+      </c>
+      <c r="M155" t="n">
+        <v>46.00317790213883</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -4030,6 +6576,24 @@
       <c r="G156" t="n">
         <v>272481512.6580482</v>
       </c>
+      <c r="H156" t="n">
+        <v>2643.6</v>
+      </c>
+      <c r="I156" t="n">
+        <v>2677.889356949323</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2609.310643050676</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-5.815759407606947</v>
+      </c>
+      <c r="L156" t="n">
+        <v>-6.286577797673916</v>
+      </c>
+      <c r="M156" t="n">
+        <v>50.62197129017851</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -4053,6 +6617,24 @@
       <c r="G157" t="n">
         <v>112516926.0449472</v>
       </c>
+      <c r="H157" t="n">
+        <v>2642.95</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2675.669871637861</v>
+      </c>
+      <c r="J157" t="n">
+        <v>2610.230128362139</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-3.795665873192775</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-5.788395412777687</v>
+      </c>
+      <c r="M157" t="n">
+        <v>54.78691520036396</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -4076,6 +6658,24 @@
       <c r="G158" t="n">
         <v>146231152.5002401</v>
       </c>
+      <c r="H158" t="n">
+        <v>2643.15</v>
+      </c>
+      <c r="I158" t="n">
+        <v>2676.522293897755</v>
+      </c>
+      <c r="J158" t="n">
+        <v>2609.777706102245</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-0.9731348604964296</v>
+      </c>
+      <c r="L158" t="n">
+        <v>-4.825343302321436</v>
+      </c>
+      <c r="M158" t="n">
+        <v>59.39718412547992</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -4099,6 +6699,24 @@
       <c r="G159" t="n">
         <v>114999363.4277045</v>
       </c>
+      <c r="H159" t="n">
+        <v>2642.75</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2674.898872452982</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2610.601127547018</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.6111630538443933</v>
+      </c>
+      <c r="L159" t="n">
+        <v>-3.73804203108827</v>
+      </c>
+      <c r="M159" t="n">
+        <v>56.11098822844568</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -4122,6 +6740,24 @@
       <c r="G160" t="n">
         <v>47825093.98570349</v>
       </c>
+      <c r="H160" t="n">
+        <v>2641.7</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2670.503472012903</v>
+      </c>
+      <c r="J160" t="n">
+        <v>2612.896527987097</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1.207280644238381</v>
+      </c>
+      <c r="L160" t="n">
+        <v>-2.748977496022941</v>
+      </c>
+      <c r="M160" t="n">
+        <v>52.95579632404529</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -4145,6 +6781,24 @@
       <c r="G161" t="n">
         <v>149582847.840915</v>
       </c>
+      <c r="H161" t="n">
+        <v>2641.7</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2670.503472012903</v>
+      </c>
+      <c r="J161" t="n">
+        <v>2612.896527987097</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1.979654475524512</v>
+      </c>
+      <c r="L161" t="n">
+        <v>-1.80325110171345</v>
+      </c>
+      <c r="M161" t="n">
+        <v>54.3383566390954</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -4168,6 +6822,24 @@
       <c r="G162" t="n">
         <v>160241620.2239336</v>
       </c>
+      <c r="H162" t="n">
+        <v>2641.55</v>
+      </c>
+      <c r="I162" t="n">
+        <v>2670.356075747975</v>
+      </c>
+      <c r="J162" t="n">
+        <v>2612.743924252025</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0.9667889077227301</v>
+      </c>
+      <c r="L162" t="n">
+        <v>-1.249243099826214</v>
+      </c>
+      <c r="M162" t="n">
+        <v>46.91434992846821</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -4191,6 +6863,24 @@
       <c r="G163" t="n">
         <v>91481626.33259143</v>
       </c>
+      <c r="H163" t="n">
+        <v>2641.2</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2670.097058673818</v>
+      </c>
+      <c r="J163" t="n">
+        <v>2612.302941326182</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-0.1568725930646906</v>
+      </c>
+      <c r="L163" t="n">
+        <v>-1.030768998473909</v>
+      </c>
+      <c r="M163" t="n">
+        <v>45.57326380927957</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -4214,6 +6904,24 @@
       <c r="G164" t="n">
         <v>57420832.10223589</v>
       </c>
+      <c r="H164" t="n">
+        <v>2640.65</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2669.196628522438</v>
+      </c>
+      <c r="J164" t="n">
+        <v>2612.103371477562</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-0.7163581268091548</v>
+      </c>
+      <c r="L164" t="n">
+        <v>-0.9678868241409586</v>
+      </c>
+      <c r="M164" t="n">
+        <v>47.19873753684605</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -4237,6 +6945,24 @@
       <c r="G165" t="n">
         <v>101387120.7287408</v>
       </c>
+      <c r="H165" t="n">
+        <v>2640.5</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2669.174030062028</v>
+      </c>
+      <c r="J165" t="n">
+        <v>2611.825969937972</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-1.704942426730213</v>
+      </c>
+      <c r="L165" t="n">
+        <v>-1.11529794465881</v>
+      </c>
+      <c r="M165" t="n">
+        <v>44.68372713381994</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -4260,6 +6986,24 @@
       <c r="G166" t="n">
         <v>36505888.09698925</v>
       </c>
+      <c r="H166" t="n">
+        <v>2641.35</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2667.619944803865</v>
+      </c>
+      <c r="J166" t="n">
+        <v>2615.080055196135</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-2.699360981634982</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-1.432110552054044</v>
+      </c>
+      <c r="M166" t="n">
+        <v>43.6111830068325</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -4283,6 +7027,24 @@
       <c r="G167" t="n">
         <v>74613999.25876261</v>
       </c>
+      <c r="H167" t="n">
+        <v>2641.55</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2667.499759151061</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2615.600240848939</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-3.208385650217224</v>
+      </c>
+      <c r="L167" t="n">
+        <v>-1.78736557168668</v>
+      </c>
+      <c r="M167" t="n">
+        <v>45.03207097320902</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -4306,6 +7068,24 @@
       <c r="G168" t="n">
         <v>245700338.6838729</v>
       </c>
+      <c r="H168" t="n">
+        <v>2642.4</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2668.936013264959</v>
+      </c>
+      <c r="J168" t="n">
+        <v>2615.863986735041</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-1.815645596824197</v>
+      </c>
+      <c r="L168" t="n">
+        <v>-1.793021576714183</v>
+      </c>
+      <c r="M168" t="n">
+        <v>54.15518646791534</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -4329,6 +7109,24 @@
       <c r="G169" t="n">
         <v>252248935.711099</v>
       </c>
+      <c r="H169" t="n">
+        <v>2643.45</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2670.854196758856</v>
+      </c>
+      <c r="J169" t="n">
+        <v>2616.045803241143</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-0.3846880553128358</v>
+      </c>
+      <c r="L169" t="n">
+        <v>-1.511354872433914</v>
+      </c>
+      <c r="M169" t="n">
+        <v>55.59815483332068</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -4352,6 +7150,24 @@
       <c r="G170" t="n">
         <v>131298352.1880191</v>
       </c>
+      <c r="H170" t="n">
+        <v>2643.75</v>
+      </c>
+      <c r="I170" t="n">
+        <v>2671.127910804116</v>
+      </c>
+      <c r="J170" t="n">
+        <v>2616.372089195884</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-0.2962206019319638</v>
+      </c>
+      <c r="L170" t="n">
+        <v>-1.268328018333524</v>
+      </c>
+      <c r="M170" t="n">
+        <v>50.08108623766994</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -4375,6 +7191,24 @@
       <c r="G171" t="n">
         <v>106766094.5649112</v>
       </c>
+      <c r="H171" t="n">
+        <v>2644.25</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2670.962356691204</v>
+      </c>
+      <c r="J171" t="n">
+        <v>2617.537643308796</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-0.7021652398598235</v>
+      </c>
+      <c r="L171" t="n">
+        <v>-1.155095462638784</v>
+      </c>
+      <c r="M171" t="n">
+        <v>47.72709114852108</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -4398,6 +7232,24 @@
       <c r="G172" t="n">
         <v>152289358.6958403</v>
       </c>
+      <c r="H172" t="n">
+        <v>2646.1</v>
+      </c>
+      <c r="I172" t="n">
+        <v>2671.19103425525</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2621.00896574475</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.4236862858651875</v>
+      </c>
+      <c r="L172" t="n">
+        <v>-0.8393391129379897</v>
+      </c>
+      <c r="M172" t="n">
+        <v>54.61861821088778</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -4421,6 +7273,24 @@
       <c r="G173" t="n">
         <v>123640316.7882359</v>
       </c>
+      <c r="H173" t="n">
+        <v>2646.75</v>
+      </c>
+      <c r="I173" t="n">
+        <v>2671.00592711067</v>
+      </c>
+      <c r="J173" t="n">
+        <v>2622.49407288933</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0.2638983212809762</v>
+      </c>
+      <c r="L173" t="n">
+        <v>-0.6186916260941965</v>
+      </c>
+      <c r="M173" t="n">
+        <v>49.53888868960065</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -4444,6 +7314,24 @@
       <c r="G174" t="n">
         <v>76624652.70232932</v>
       </c>
+      <c r="H174" t="n">
+        <v>2646.9</v>
+      </c>
+      <c r="I174" t="n">
+        <v>2670.84911271839</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2622.95088728161</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-0.5822477856872865</v>
+      </c>
+      <c r="L174" t="n">
+        <v>-0.6114028580128146</v>
+      </c>
+      <c r="M174" t="n">
+        <v>46.32660291230825</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -4467,6 +7355,24 @@
       <c r="G175" t="n">
         <v>85490263.49955657</v>
       </c>
+      <c r="H175" t="n">
+        <v>2647.25</v>
+      </c>
+      <c r="I175" t="n">
+        <v>2670.572735688554</v>
+      </c>
+      <c r="J175" t="n">
+        <v>2623.927264311446</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-0.919459148290116</v>
+      </c>
+      <c r="L175" t="n">
+        <v>-0.6730141160682749</v>
+      </c>
+      <c r="M175" t="n">
+        <v>47.94228237161023</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -4490,6 +7396,24 @@
       <c r="G176" t="n">
         <v>115627497.3361659</v>
       </c>
+      <c r="H176" t="n">
+        <v>2646.8</v>
+      </c>
+      <c r="I176" t="n">
+        <v>2670.620999139376</v>
+      </c>
+      <c r="J176" t="n">
+        <v>2622.979000860624</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-1.49226623695813</v>
+      </c>
+      <c r="L176" t="n">
+        <v>-0.836864540246246</v>
+      </c>
+      <c r="M176" t="n">
+        <v>46.43690940988297</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -4513,6 +7437,24 @@
       <c r="G177" t="n">
         <v>27244619.85346802</v>
       </c>
+      <c r="H177" t="n">
+        <v>2646.3</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2669.658938332</v>
+      </c>
+      <c r="J177" t="n">
+        <v>2622.941061668001</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-1.046547958997962</v>
+      </c>
+      <c r="L177" t="n">
+        <v>-0.8788012239965892</v>
+      </c>
+      <c r="M177" t="n">
+        <v>50.99404201841028</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -4536,6 +7478,24 @@
       <c r="G178" t="n">
         <v>84985202.98413876</v>
       </c>
+      <c r="H178" t="n">
+        <v>2644.75</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2664.987341722621</v>
+      </c>
+      <c r="J178" t="n">
+        <v>2624.512658277379</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-1.164044488128638</v>
+      </c>
+      <c r="L178" t="n">
+        <v>-0.935849876822999</v>
+      </c>
+      <c r="M178" t="n">
+        <v>48.56682291614425</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -4559,6 +7519,24 @@
       <c r="G179" t="n">
         <v>34240755.03090711</v>
       </c>
+      <c r="H179" t="n">
+        <v>2644.1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>2662.581341942568</v>
+      </c>
+      <c r="J179" t="n">
+        <v>2625.618658057432</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-0.4451139113721183</v>
+      </c>
+      <c r="L179" t="n">
+        <v>-0.837702683732823</v>
+      </c>
+      <c r="M179" t="n">
+        <v>52.61503744017277</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -4582,6 +7560,24 @@
       <c r="G180" t="n">
         <v>105202176.4314434</v>
       </c>
+      <c r="H180" t="n">
+        <v>2643.6</v>
+      </c>
+      <c r="I180" t="n">
+        <v>2661.290675509944</v>
+      </c>
+      <c r="J180" t="n">
+        <v>2625.909324490056</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-0.2756370901370246</v>
+      </c>
+      <c r="L180" t="n">
+        <v>-0.7252895650136634</v>
+      </c>
+      <c r="M180" t="n">
+        <v>50.47580437379541</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -4605,6 +7601,24 @@
       <c r="G181" t="n">
         <v>113888703.7378861</v>
       </c>
+      <c r="H181" t="n">
+        <v>2643.45</v>
+      </c>
+      <c r="I181" t="n">
+        <v>2660.625272923541</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2626.274727076458</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0.737777936074508</v>
+      </c>
+      <c r="L181" t="n">
+        <v>-0.4326760647960292</v>
+      </c>
+      <c r="M181" t="n">
+        <v>54.82723676906337</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -4628,6 +7642,24 @@
       <c r="G182" t="n">
         <v>147459486.0117355</v>
       </c>
+      <c r="H182" t="n">
+        <v>2644.5</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2663.20294094516</v>
+      </c>
+      <c r="J182" t="n">
+        <v>2625.79705905484</v>
+      </c>
+      <c r="K182" t="n">
+        <v>1.842444661042464</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.02234808037166941</v>
+      </c>
+      <c r="M182" t="n">
+        <v>56.32986429835302</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -4651,6 +7683,24 @@
       <c r="G183" t="n">
         <v>324783535.4269731</v>
       </c>
+      <c r="H183" t="n">
+        <v>2645.95</v>
+      </c>
+      <c r="I183" t="n">
+        <v>2666.222888299355</v>
+      </c>
+      <c r="J183" t="n">
+        <v>2625.677111700644</v>
+      </c>
+      <c r="K183" t="n">
+        <v>3.006016087600983</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.6190816818175322</v>
+      </c>
+      <c r="M183" t="n">
+        <v>57.84014769518307</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -4674,6 +7724,24 @@
       <c r="G184" t="n">
         <v>207090409.3193978</v>
       </c>
+      <c r="H184" t="n">
+        <v>2647.85</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2672.240776945357</v>
+      </c>
+      <c r="J184" t="n">
+        <v>2623.459223054643</v>
+      </c>
+      <c r="K184" t="n">
+        <v>4.920426566100105</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1.479350658674047</v>
+      </c>
+      <c r="M184" t="n">
+        <v>62.3923181442958</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -4697,6 +7765,24 @@
       <c r="G185" t="n">
         <v>556450197.0867641</v>
       </c>
+      <c r="H185" t="n">
+        <v>2651.1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>2682.905031048534</v>
+      </c>
+      <c r="J185" t="n">
+        <v>2619.294968951466</v>
+      </c>
+      <c r="K185" t="n">
+        <v>7.959689173857896</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2.775418361710817</v>
+      </c>
+      <c r="M185" t="n">
+        <v>68.09912703089365</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -4720,6 +7806,24 @@
       <c r="G186" t="n">
         <v>539746250.2727349</v>
       </c>
+      <c r="H186" t="n">
+        <v>2654.8</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2692.58147694305</v>
+      </c>
+      <c r="J186" t="n">
+        <v>2617.01852305695</v>
+      </c>
+      <c r="K186" t="n">
+        <v>10.72880159675788</v>
+      </c>
+      <c r="L186" t="n">
+        <v>4.366095008720229</v>
+      </c>
+      <c r="M186" t="n">
+        <v>69.589995033018</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -4743,6 +7847,24 @@
       <c r="G187" t="n">
         <v>528340350.9267045</v>
       </c>
+      <c r="H187" t="n">
+        <v>2657</v>
+      </c>
+      <c r="I187" t="n">
+        <v>2694.571265616136</v>
+      </c>
+      <c r="J187" t="n">
+        <v>2619.428734383864</v>
+      </c>
+      <c r="K187" t="n">
+        <v>10.62222242271355</v>
+      </c>
+      <c r="L187" t="n">
+        <v>5.617320491518893</v>
+      </c>
+      <c r="M187" t="n">
+        <v>56.73951279871584</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -4766,6 +7888,24 @@
       <c r="G188" t="n">
         <v>231599647.7135401</v>
       </c>
+      <c r="H188" t="n">
+        <v>2657.75</v>
+      </c>
+      <c r="I188" t="n">
+        <v>2695.728283268182</v>
+      </c>
+      <c r="J188" t="n">
+        <v>2619.771716731818</v>
+      </c>
+      <c r="K188" t="n">
+        <v>9.859264694642661</v>
+      </c>
+      <c r="L188" t="n">
+        <v>6.465709332143646</v>
+      </c>
+      <c r="M188" t="n">
+        <v>53.95759579074381</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -4789,6 +7929,24 @@
       <c r="G189" t="n">
         <v>185864830.7997025</v>
       </c>
+      <c r="H189" t="n">
+        <v>2658.25</v>
+      </c>
+      <c r="I189" t="n">
+        <v>2696.542949742717</v>
+      </c>
+      <c r="J189" t="n">
+        <v>2619.957050257283</v>
+      </c>
+      <c r="K189" t="n">
+        <v>9.069377418294607</v>
+      </c>
+      <c r="L189" t="n">
+        <v>6.986442949373838</v>
+      </c>
+      <c r="M189" t="n">
+        <v>53.55363966085852</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -4812,6 +7970,24 @@
       <c r="G190" t="n">
         <v>333033311.98533</v>
       </c>
+      <c r="H190" t="n">
+        <v>2658.9</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2696.778225935202</v>
+      </c>
+      <c r="J190" t="n">
+        <v>2621.021774064798</v>
+      </c>
+      <c r="K190" t="n">
+        <v>7.549444339465936</v>
+      </c>
+      <c r="L190" t="n">
+        <v>7.099043227392258</v>
+      </c>
+      <c r="M190" t="n">
+        <v>49.55805319614869</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -4835,6 +8011,24 @@
       <c r="G191" t="n">
         <v>252868269.267511</v>
       </c>
+      <c r="H191" t="n">
+        <v>2660.55</v>
+      </c>
+      <c r="I191" t="n">
+        <v>2697.86206239272</v>
+      </c>
+      <c r="J191" t="n">
+        <v>2623.23793760728</v>
+      </c>
+      <c r="K191" t="n">
+        <v>7.38938914278242</v>
+      </c>
+      <c r="L191" t="n">
+        <v>7.157112410470291</v>
+      </c>
+      <c r="M191" t="n">
+        <v>54.65841471669736</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -4858,6 +8052,24 @@
       <c r="G192" t="n">
         <v>179680414.8334219</v>
       </c>
+      <c r="H192" t="n">
+        <v>2661.15</v>
+      </c>
+      <c r="I192" t="n">
+        <v>2698.664130670965</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2623.635869329035</v>
+      </c>
+      <c r="K192" t="n">
+        <v>6.940463969965094</v>
+      </c>
+      <c r="L192" t="n">
+        <v>7.113782722369253</v>
+      </c>
+      <c r="M192" t="n">
+        <v>53.41210293513458</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -4881,6 +8093,24 @@
       <c r="G193" t="n">
         <v>337553766.360055</v>
       </c>
+      <c r="H193" t="n">
+        <v>2662.5</v>
+      </c>
+      <c r="I193" t="n">
+        <v>2699.532418230495</v>
+      </c>
+      <c r="J193" t="n">
+        <v>2625.467581769505</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6.669192521518198</v>
+      </c>
+      <c r="L193" t="n">
+        <v>7.024864682199042</v>
+      </c>
+      <c r="M193" t="n">
+        <v>54.16248791229241</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -4904,6 +8134,24 @@
       <c r="G194" t="n">
         <v>155498948.742183</v>
       </c>
+      <c r="H194" t="n">
+        <v>2664.7</v>
+      </c>
+      <c r="I194" t="n">
+        <v>2700.376883271921</v>
+      </c>
+      <c r="J194" t="n">
+        <v>2629.023116728079</v>
+      </c>
+      <c r="K194" t="n">
+        <v>7.018832355111044</v>
+      </c>
+      <c r="L194" t="n">
+        <v>7.023658216781443</v>
+      </c>
+      <c r="M194" t="n">
+        <v>57.13650383698428</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -4927,6 +8175,24 @@
       <c r="G195" t="n">
         <v>382449391.7712592</v>
       </c>
+      <c r="H195" t="n">
+        <v>2666.6</v>
+      </c>
+      <c r="I195" t="n">
+        <v>2700.830980120328</v>
+      </c>
+      <c r="J195" t="n">
+        <v>2632.369019879672</v>
+      </c>
+      <c r="K195" t="n">
+        <v>7.053235844619849</v>
+      </c>
+      <c r="L195" t="n">
+        <v>7.029573742349124</v>
+      </c>
+      <c r="M195" t="n">
+        <v>56.15556984807701</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -4950,6 +8216,24 @@
       <c r="G196" t="n">
         <v>309710793.3388847</v>
       </c>
+      <c r="H196" t="n">
+        <v>2668.35</v>
+      </c>
+      <c r="I196" t="n">
+        <v>2699.592759161097</v>
+      </c>
+      <c r="J196" t="n">
+        <v>2637.107240838903</v>
+      </c>
+      <c r="K196" t="n">
+        <v>6.44140683104888</v>
+      </c>
+      <c r="L196" t="n">
+        <v>6.911940360089075</v>
+      </c>
+      <c r="M196" t="n">
+        <v>52.74254145657387</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -4973,6 +8257,24 @@
       <c r="G197" t="n">
         <v>417444970.9107422</v>
       </c>
+      <c r="H197" t="n">
+        <v>2668.9</v>
+      </c>
+      <c r="I197" t="n">
+        <v>2698.985877085408</v>
+      </c>
+      <c r="J197" t="n">
+        <v>2638.814122914592</v>
+      </c>
+      <c r="K197" t="n">
+        <v>4.851610232598432</v>
+      </c>
+      <c r="L197" t="n">
+        <v>6.499874334590947</v>
+      </c>
+      <c r="M197" t="n">
+        <v>47.02621429704395</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -4996,6 +8298,24 @@
       <c r="G198" t="n">
         <v>164903027.7084528</v>
       </c>
+      <c r="H198" t="n">
+        <v>2669.8</v>
+      </c>
+      <c r="I198" t="n">
+        <v>2697.473814337715</v>
+      </c>
+      <c r="J198" t="n">
+        <v>2642.126185662285</v>
+      </c>
+      <c r="K198" t="n">
+        <v>3.630526171331894</v>
+      </c>
+      <c r="L198" t="n">
+        <v>5.926004701939137</v>
+      </c>
+      <c r="M198" t="n">
+        <v>47.49760011276945</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -5019,6 +8339,24 @@
       <c r="G199" t="n">
         <v>202482162.0059156</v>
       </c>
+      <c r="H199" t="n">
+        <v>2670.05</v>
+      </c>
+      <c r="I199" t="n">
+        <v>2697.123788061487</v>
+      </c>
+      <c r="J199" t="n">
+        <v>2642.976211938513</v>
+      </c>
+      <c r="K199" t="n">
+        <v>2.393146622803215</v>
+      </c>
+      <c r="L199" t="n">
+        <v>5.219433086111953</v>
+      </c>
+      <c r="M199" t="n">
+        <v>46.17025542769301</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -5042,6 +8380,24 @@
       <c r="G200" t="n">
         <v>138915332.1906864</v>
       </c>
+      <c r="H200" t="n">
+        <v>2670.15</v>
+      </c>
+      <c r="I200" t="n">
+        <v>2696.880319863375</v>
+      </c>
+      <c r="J200" t="n">
+        <v>2643.419680136626</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0.7582407472000341</v>
+      </c>
+      <c r="L200" t="n">
+        <v>4.327194618329569</v>
+      </c>
+      <c r="M200" t="n">
+        <v>42.74019359496302</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -5065,6 +8421,24 @@
       <c r="G201" t="n">
         <v>136971345.834191</v>
       </c>
+      <c r="H201" t="n">
+        <v>2669.8</v>
+      </c>
+      <c r="I201" t="n">
+        <v>2697.37970268147</v>
+      </c>
+      <c r="J201" t="n">
+        <v>2642.22029731853</v>
+      </c>
+      <c r="K201" t="n">
+        <v>-0.3717651752490383</v>
+      </c>
+      <c r="L201" t="n">
+        <v>3.387402659613848</v>
+      </c>
+      <c r="M201" t="n">
+        <v>43.86302200709348</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -5088,6 +8462,24 @@
       <c r="G202" t="n">
         <v>135775606.4701379</v>
       </c>
+      <c r="H202" t="n">
+        <v>2668.95</v>
+      </c>
+      <c r="I202" t="n">
+        <v>2698.53699038426</v>
+      </c>
+      <c r="J202" t="n">
+        <v>2639.363009615739</v>
+      </c>
+      <c r="K202" t="n">
+        <v>-1.731493289130412</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2.363623469864996</v>
+      </c>
+      <c r="M202" t="n">
+        <v>41.24971513793474</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -5111,6 +8503,24 @@
       <c r="G203" t="n">
         <v>384317449.8017954</v>
       </c>
+      <c r="H203" t="n">
+        <v>2667.5</v>
+      </c>
+      <c r="I203" t="n">
+        <v>2700.378564445522</v>
+      </c>
+      <c r="J203" t="n">
+        <v>2634.621435554478</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-3.415251859389627</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1.207848404014071</v>
+      </c>
+      <c r="M203" t="n">
+        <v>37.99894115429232</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -5134,6 +8544,24 @@
       <c r="G204" t="n">
         <v>239215961.658834</v>
       </c>
+      <c r="H204" t="n">
+        <v>2664.95</v>
+      </c>
+      <c r="I204" t="n">
+        <v>2701.841597959404</v>
+      </c>
+      <c r="J204" t="n">
+        <v>2628.058402040596</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-5.413464393246159</v>
+      </c>
+      <c r="L204" t="n">
+        <v>-0.1164141554379747</v>
+      </c>
+      <c r="M204" t="n">
+        <v>34.6870894103462</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -5157,6 +8585,24 @@
       <c r="G205" t="n">
         <v>1312829774.230139</v>
       </c>
+      <c r="H205" t="n">
+        <v>2663.15</v>
+      </c>
+      <c r="I205" t="n">
+        <v>2696.784952058808</v>
+      </c>
+      <c r="J205" t="n">
+        <v>2629.515047941192</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-4.125300829820389</v>
+      </c>
+      <c r="L205" t="n">
+        <v>-0.9181914903144577</v>
+      </c>
+      <c r="M205" t="n">
+        <v>52.15220720435757</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -5180,6 +8626,24 @@
       <c r="G206" t="n">
         <v>1635896143.436514</v>
       </c>
+      <c r="H206" t="n">
+        <v>2662.7</v>
+      </c>
+      <c r="I206" t="n">
+        <v>2694.317083989487</v>
+      </c>
+      <c r="J206" t="n">
+        <v>2631.082916010512</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-0.4365652649730691</v>
+      </c>
+      <c r="L206" t="n">
+        <v>-0.82186624524618</v>
+      </c>
+      <c r="M206" t="n">
+        <v>62.36963339956469</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -5203,6 +8667,24 @@
       <c r="G207" t="n">
         <v>708570431.9114646</v>
       </c>
+      <c r="H207" t="n">
+        <v>2663.2</v>
+      </c>
+      <c r="I207" t="n">
+        <v>2695.999999999974</v>
+      </c>
+      <c r="J207" t="n">
+        <v>2630.400000000026</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1.820268186288558</v>
+      </c>
+      <c r="L207" t="n">
+        <v>-0.2934393589392323</v>
+      </c>
+      <c r="M207" t="n">
+        <v>59.07617128442359</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -5226,6 +8708,24 @@
       <c r="G208" t="n">
         <v>1442152888.250826</v>
       </c>
+      <c r="H208" t="n">
+        <v>2666.15</v>
+      </c>
+      <c r="I208" t="n">
+        <v>2709.712713414092</v>
+      </c>
+      <c r="J208" t="n">
+        <v>2622.587286585908</v>
+      </c>
+      <c r="K208" t="n">
+        <v>6.918126096122705</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1.148873732073155</v>
+      </c>
+      <c r="M208" t="n">
+        <v>68.48508703204192</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -5249,6 +8749,24 @@
       <c r="G209" t="n">
         <v>1309602454.335502</v>
       </c>
+      <c r="H209" t="n">
+        <v>2669</v>
+      </c>
+      <c r="I209" t="n">
+        <v>2719.793700396785</v>
+      </c>
+      <c r="J209" t="n">
+        <v>2618.206299603215</v>
+      </c>
+      <c r="K209" t="n">
+        <v>10.5940190329311</v>
+      </c>
+      <c r="L209" t="n">
+        <v>3.037902792244744</v>
+      </c>
+      <c r="M209" t="n">
+        <v>67.2949352569281</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -5272,6 +8790,24 @@
       <c r="G210" t="n">
         <v>1531565811.79616</v>
       </c>
+      <c r="H210" t="n">
+        <v>2672.7</v>
+      </c>
+      <c r="I210" t="n">
+        <v>2730.357956953038</v>
+      </c>
+      <c r="J210" t="n">
+        <v>2615.042043046962</v>
+      </c>
+      <c r="K210" t="n">
+        <v>13.91166712834638</v>
+      </c>
+      <c r="L210" t="n">
+        <v>5.212655659465072</v>
+      </c>
+      <c r="M210" t="n">
+        <v>68.66335793343823</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -5295,6 +8831,24 @@
       <c r="G211" t="n">
         <v>3272538694.008086</v>
       </c>
+      <c r="H211" t="n">
+        <v>2676.35</v>
+      </c>
+      <c r="I211" t="n">
+        <v>2742.271999362871</v>
+      </c>
+      <c r="J211" t="n">
+        <v>2610.428000637129</v>
+      </c>
+      <c r="K211" t="n">
+        <v>17.3894635891038</v>
+      </c>
+      <c r="L211" t="n">
+        <v>7.648017245392817</v>
+      </c>
+      <c r="M211" t="n">
+        <v>71.08319205035244</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -5318,6 +8872,24 @@
       <c r="G212" t="n">
         <v>2932904584.334806</v>
       </c>
+      <c r="H212" t="n">
+        <v>2677.85</v>
+      </c>
+      <c r="I212" t="n">
+        <v>2744.487151799866</v>
+      </c>
+      <c r="J212" t="n">
+        <v>2611.212848200134</v>
+      </c>
+      <c r="K212" t="n">
+        <v>16.24654670121708</v>
+      </c>
+      <c r="L212" t="n">
+        <v>9.367723136557672</v>
+      </c>
+      <c r="M212" t="n">
+        <v>54.92184894169657</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -5341,6 +8913,24 @@
       <c r="G213" t="n">
         <v>419466656.9481533</v>
       </c>
+      <c r="H213" t="n">
+        <v>2678.85</v>
+      </c>
+      <c r="I213" t="n">
+        <v>2745.705889792885</v>
+      </c>
+      <c r="J213" t="n">
+        <v>2611.994110207115</v>
+      </c>
+      <c r="K213" t="n">
+        <v>14.52777652750319</v>
+      </c>
+      <c r="L213" t="n">
+        <v>10.39973381474678</v>
+      </c>
+      <c r="M213" t="n">
+        <v>52.67867867164113</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -5364,6 +8954,24 @@
       <c r="G214" t="n">
         <v>369651482.7920932</v>
       </c>
+      <c r="H214" t="n">
+        <v>2678.7</v>
+      </c>
+      <c r="I214" t="n">
+        <v>2745.558357742308</v>
+      </c>
+      <c r="J214" t="n">
+        <v>2611.841642257692</v>
+      </c>
+      <c r="K214" t="n">
+        <v>11.81902181559053</v>
+      </c>
+      <c r="L214" t="n">
+        <v>10.68359141491553</v>
+      </c>
+      <c r="M214" t="n">
+        <v>48.66519488063358</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -5387,6 +8995,24 @@
       <c r="G215" t="n">
         <v>532125373.9059793</v>
       </c>
+      <c r="H215" t="n">
+        <v>2678.25</v>
+      </c>
+      <c r="I215" t="n">
+        <v>2745.242163720829</v>
+      </c>
+      <c r="J215" t="n">
+        <v>2611.257836279171</v>
+      </c>
+      <c r="K215" t="n">
+        <v>8.923911749954641</v>
+      </c>
+      <c r="L215" t="n">
+        <v>10.33165548192335</v>
+      </c>
+      <c r="M215" t="n">
+        <v>46.62492239209811</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -5410,6 +9036,24 @@
       <c r="G216" t="n">
         <v>738679105.8370532</v>
       </c>
+      <c r="H216" t="n">
+        <v>2678.7</v>
+      </c>
+      <c r="I216" t="n">
+        <v>2745.612181252731</v>
+      </c>
+      <c r="J216" t="n">
+        <v>2611.787818747268</v>
+      </c>
+      <c r="K216" t="n">
+        <v>7.431459000524683</v>
+      </c>
+      <c r="L216" t="n">
+        <v>9.751616185643618</v>
+      </c>
+      <c r="M216" t="n">
+        <v>49.74480363068961</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -5433,6 +9077,24 @@
       <c r="G217" t="n">
         <v>2168452747.327362</v>
       </c>
+      <c r="H217" t="n">
+        <v>2677.55</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2746.602081793371</v>
+      </c>
+      <c r="J217" t="n">
+        <v>2608.497918206629</v>
+      </c>
+      <c r="K217" t="n">
+        <v>2.587725832161595</v>
+      </c>
+      <c r="L217" t="n">
+        <v>8.318838114947214</v>
+      </c>
+      <c r="M217" t="n">
+        <v>39.55799166833316</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -5456,6 +9118,24 @@
       <c r="G218" t="n">
         <v>1714769711.371104</v>
       </c>
+      <c r="H218" t="n">
+        <v>2675.45</v>
+      </c>
+      <c r="I218" t="n">
+        <v>2749.036615630822</v>
+      </c>
+      <c r="J218" t="n">
+        <v>2601.863384369177</v>
+      </c>
+      <c r="K218" t="n">
+        <v>-2.6726089958388</v>
+      </c>
+      <c r="L218" t="n">
+        <v>6.120548692790011</v>
+      </c>
+      <c r="M218" t="n">
+        <v>36.35131365930265</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -5479,6 +9159,24 @@
       <c r="G219" t="n">
         <v>494872293.5021561</v>
       </c>
+      <c r="H219" t="n">
+        <v>2673.9</v>
+      </c>
+      <c r="I219" t="n">
+        <v>2750.311779196655</v>
+      </c>
+      <c r="J219" t="n">
+        <v>2597.488220803345</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-6.125320225801715</v>
+      </c>
+      <c r="L219" t="n">
+        <v>3.671374909071667</v>
+      </c>
+      <c r="M219" t="n">
+        <v>38.72859785406573</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -5502,6 +9200,24 @@
       <c r="G220" t="n">
         <v>597090923.5315993</v>
       </c>
+      <c r="H220" t="n">
+        <v>2674</v>
+      </c>
+      <c r="I220" t="n">
+        <v>2750.28105924801</v>
+      </c>
+      <c r="J220" t="n">
+        <v>2597.71894075199</v>
+      </c>
+      <c r="K220" t="n">
+        <v>-6.766329648412921</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1.583833997574749</v>
+      </c>
+      <c r="M220" t="n">
+        <v>45.57027398239693</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -5525,6 +9241,24 @@
       <c r="G221" t="n">
         <v>618290087.0417094</v>
       </c>
+      <c r="H221" t="n">
+        <v>2673.8</v>
+      </c>
+      <c r="I221" t="n">
+        <v>2750.352204409791</v>
+      </c>
+      <c r="J221" t="n">
+        <v>2597.24779559021</v>
+      </c>
+      <c r="K221" t="n">
+        <v>-7.510524157314649</v>
+      </c>
+      <c r="L221" t="n">
+        <v>-0.2350376334031301</v>
+      </c>
+      <c r="M221" t="n">
+        <v>44.710044231845</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -5548,6 +9282,24 @@
       <c r="G222" t="n">
         <v>260989427.0964765</v>
       </c>
+      <c r="H222" t="n">
+        <v>2673.8</v>
+      </c>
+      <c r="I222" t="n">
+        <v>2750.352204409791</v>
+      </c>
+      <c r="J222" t="n">
+        <v>2597.24779559021</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-8.167536673891391</v>
+      </c>
+      <c r="L222" t="n">
+        <v>-1.821537441500782</v>
+      </c>
+      <c r="M222" t="n">
+        <v>44.2601602930955</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -5571,6 +9323,24 @@
       <c r="G223" t="n">
         <v>565871252.5659508</v>
       </c>
+      <c r="H223" t="n">
+        <v>2675.2</v>
+      </c>
+      <c r="I223" t="n">
+        <v>2749.938477372759</v>
+      </c>
+      <c r="J223" t="n">
+        <v>2600.461522627241</v>
+      </c>
+      <c r="K223" t="n">
+        <v>-6.99377113361561</v>
+      </c>
+      <c r="L223" t="n">
+        <v>-2.855984179923748</v>
+      </c>
+      <c r="M223" t="n">
+        <v>49.70975069256939</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -5594,6 +9364,24 @@
       <c r="G224" t="n">
         <v>707044543.7933191</v>
       </c>
+      <c r="H224" t="n">
+        <v>2675.95</v>
+      </c>
+      <c r="I224" t="n">
+        <v>2749.021129729862</v>
+      </c>
+      <c r="J224" t="n">
+        <v>2602.878870270137</v>
+      </c>
+      <c r="K224" t="n">
+        <v>-7.749438916776853</v>
+      </c>
+      <c r="L224" t="n">
+        <v>-3.83467512729437</v>
+      </c>
+      <c r="M224" t="n">
+        <v>44.55005851219128</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -5617,6 +9405,24 @@
       <c r="G225" t="n">
         <v>447749971.3528119</v>
       </c>
+      <c r="H225" t="n">
+        <v>2674.3</v>
+      </c>
+      <c r="I225" t="n">
+        <v>2749.999669748278</v>
+      </c>
+      <c r="J225" t="n">
+        <v>2598.600330251722</v>
+      </c>
+      <c r="K225" t="n">
+        <v>-9.290210668065356</v>
+      </c>
+      <c r="L225" t="n">
+        <v>-4.925782235448567</v>
+      </c>
+      <c r="M225" t="n">
+        <v>41.78975172177689</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -5640,6 +9446,24 @@
       <c r="G226" t="n">
         <v>290864053.7128338</v>
       </c>
+      <c r="H226" t="n">
+        <v>2671.45</v>
+      </c>
+      <c r="I226" t="n">
+        <v>2748.103701802316</v>
+      </c>
+      <c r="J226" t="n">
+        <v>2594.796298197684</v>
+      </c>
+      <c r="K226" t="n">
+        <v>-9.673547958470408</v>
+      </c>
+      <c r="L226" t="n">
+        <v>-5.875335380052936</v>
+      </c>
+      <c r="M226" t="n">
+        <v>44.36002805808589</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -5663,6 +9487,24 @@
       <c r="G227" t="n">
         <v>529867599.0541822</v>
       </c>
+      <c r="H227" t="n">
+        <v>2668.05</v>
+      </c>
+      <c r="I227" t="n">
+        <v>2747.620032047237</v>
+      </c>
+      <c r="J227" t="n">
+        <v>2588.479967952763</v>
+      </c>
+      <c r="K227" t="n">
+        <v>-11.37931309530086</v>
+      </c>
+      <c r="L227" t="n">
+        <v>-6.97613092310252</v>
+      </c>
+      <c r="M227" t="n">
+        <v>40.31312665055714</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -5686,6 +9528,24 @@
       <c r="G228" t="n">
         <v>410749378.0248039</v>
       </c>
+      <c r="H228" t="n">
+        <v>2662.65</v>
+      </c>
+      <c r="I228" t="n">
+        <v>2739.555851532886</v>
+      </c>
+      <c r="J228" t="n">
+        <v>2585.744148467114</v>
+      </c>
+      <c r="K228" t="n">
+        <v>-12.42651583104816</v>
+      </c>
+      <c r="L228" t="n">
+        <v>-8.066207904691648</v>
+      </c>
+      <c r="M228" t="n">
+        <v>40.92407211025944</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -5709,6 +9569,24 @@
       <c r="G229" t="n">
         <v>380359593.007575</v>
       </c>
+      <c r="H229" t="n">
+        <v>2656.45</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2731.907206415281</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2580.992793584719</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-14.62103061454172</v>
+      </c>
+      <c r="L229" t="n">
+        <v>-9.377172446661664</v>
+      </c>
+      <c r="M229" t="n">
+        <v>37.04472794567692</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -5732,6 +9610,24 @@
       <c r="G230" t="n">
         <v>315460594.8815131</v>
       </c>
+      <c r="H230" t="n">
+        <v>2649.7</v>
+      </c>
+      <c r="I230" t="n">
+        <v>2720.571997290878</v>
+      </c>
+      <c r="J230" t="n">
+        <v>2578.828002709122</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-16.4928466914721</v>
+      </c>
+      <c r="L230" t="n">
+        <v>-10.80030729562375</v>
+      </c>
+      <c r="M230" t="n">
+        <v>36.26532486960789</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -5755,6 +9651,24 @@
       <c r="G231" t="n">
         <v>133589578.5871992</v>
       </c>
+      <c r="H231" t="n">
+        <v>2642.9</v>
+      </c>
+      <c r="I231" t="n">
+        <v>2700.331350323653</v>
+      </c>
+      <c r="J231" t="n">
+        <v>2585.468649676347</v>
+      </c>
+      <c r="K231" t="n">
+        <v>-16.81415163275415</v>
+      </c>
+      <c r="L231" t="n">
+        <v>-12.00307616304983</v>
+      </c>
+      <c r="M231" t="n">
+        <v>40.32187470570734</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -5778,6 +9692,24 @@
       <c r="G232" t="n">
         <v>805225294.792551</v>
       </c>
+      <c r="H232" t="n">
+        <v>2640.55</v>
+      </c>
+      <c r="I232" t="n">
+        <v>2691.975577293776</v>
+      </c>
+      <c r="J232" t="n">
+        <v>2589.124422706224</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-13.44407257953935</v>
+      </c>
+      <c r="L232" t="n">
+        <v>-12.29127544634774</v>
+      </c>
+      <c r="M232" t="n">
+        <v>52.08938697995151</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -5801,6 +9733,24 @@
       <c r="G233" t="n">
         <v>383078281.3708243</v>
       </c>
+      <c r="H233" t="n">
+        <v>2638.25</v>
+      </c>
+      <c r="I233" t="n">
+        <v>2684.075211401565</v>
+      </c>
+      <c r="J233" t="n">
+        <v>2592.424788598435</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-11.20889300702538</v>
+      </c>
+      <c r="L233" t="n">
+        <v>-12.07479895848327</v>
+      </c>
+      <c r="M233" t="n">
+        <v>50.34888851914756</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -5824,6 +9774,24 @@
       <c r="G234" t="n">
         <v>230742384.346044</v>
       </c>
+      <c r="H234" t="n">
+        <v>2635.75</v>
+      </c>
+      <c r="I234" t="n">
+        <v>2678.175817611427</v>
+      </c>
+      <c r="J234" t="n">
+        <v>2593.324182388573</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-10.84561678346608</v>
+      </c>
+      <c r="L234" t="n">
+        <v>-11.82896252347983</v>
+      </c>
+      <c r="M234" t="n">
+        <v>45.86884299625617</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -5847,6 +9815,24 @@
       <c r="G235" t="n">
         <v>477581053.9463603</v>
       </c>
+      <c r="H235" t="n">
+        <v>2633.3</v>
+      </c>
+      <c r="I235" t="n">
+        <v>2673.355461550182</v>
+      </c>
+      <c r="J235" t="n">
+        <v>2593.244538449819</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-10.99580644553862</v>
+      </c>
+      <c r="L235" t="n">
+        <v>-11.66233130789159</v>
+      </c>
+      <c r="M235" t="n">
+        <v>44.30471736751217</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -5870,6 +9856,24 @@
       <c r="G236" t="n">
         <v>423521662.2303279</v>
       </c>
+      <c r="H236" t="n">
+        <v>2631.5</v>
+      </c>
+      <c r="I236" t="n">
+        <v>2665.824918062511</v>
+      </c>
+      <c r="J236" t="n">
+        <v>2597.175081937489</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-9.073638158608446</v>
+      </c>
+      <c r="L236" t="n">
+        <v>-11.14459267803496</v>
+      </c>
+      <c r="M236" t="n">
+        <v>50.53298716395069</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -5893,6 +9897,24 @@
       <c r="G237" t="n">
         <v>554894066.4151206</v>
       </c>
+      <c r="H237" t="n">
+        <v>2633.5</v>
+      </c>
+      <c r="I237" t="n">
+        <v>2672.719892911609</v>
+      </c>
+      <c r="J237" t="n">
+        <v>2594.280107088391</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-4.991328097240967</v>
+      </c>
+      <c r="L237" t="n">
+        <v>-9.913939761876163</v>
+      </c>
+      <c r="M237" t="n">
+        <v>57.19198973430703</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -5916,6 +9938,24 @@
       <c r="G238" t="n">
         <v>2312218713.835152</v>
       </c>
+      <c r="H238" t="n">
+        <v>2639.2</v>
+      </c>
+      <c r="I238" t="n">
+        <v>2696.252957854945</v>
+      </c>
+      <c r="J238" t="n">
+        <v>2582.147042145055</v>
+      </c>
+      <c r="K238" t="n">
+        <v>2.731180675594715</v>
+      </c>
+      <c r="L238" t="n">
+        <v>-7.384915674381988</v>
+      </c>
+      <c r="M238" t="n">
+        <v>66.07604079435561</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -5939,6 +9979,24 @@
       <c r="G239" t="n">
         <v>741370159.4579858</v>
       </c>
+      <c r="H239" t="n">
+        <v>2643.7</v>
+      </c>
+      <c r="I239" t="n">
+        <v>2709.143410669051</v>
+      </c>
+      <c r="J239" t="n">
+        <v>2578.256589330948</v>
+      </c>
+      <c r="K239" t="n">
+        <v>7.474101444333428</v>
+      </c>
+      <c r="L239" t="n">
+        <v>-4.413112250638905</v>
+      </c>
+      <c r="M239" t="n">
+        <v>62.10993995366516</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -5962,6 +10020,24 @@
       <c r="G240" t="n">
         <v>646964814.1129154</v>
       </c>
+      <c r="H240" t="n">
+        <v>2647.55</v>
+      </c>
+      <c r="I240" t="n">
+        <v>2722.405794698862</v>
+      </c>
+      <c r="J240" t="n">
+        <v>2572.694205301138</v>
+      </c>
+      <c r="K240" t="n">
+        <v>12.06215502161467</v>
+      </c>
+      <c r="L240" t="n">
+        <v>-1.11805879618819</v>
+      </c>
+      <c r="M240" t="n">
+        <v>63.86192617816987</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -5985,6 +10061,24 @@
       <c r="G241" t="n">
         <v>2692215668.67658</v>
       </c>
+      <c r="H241" t="n">
+        <v>2653.65</v>
+      </c>
+      <c r="I241" t="n">
+        <v>2745.059572802843</v>
+      </c>
+      <c r="J241" t="n">
+        <v>2562.240427197157</v>
+      </c>
+      <c r="K241" t="n">
+        <v>18.78997870727244</v>
+      </c>
+      <c r="L241" t="n">
+        <v>2.863548704503937</v>
+      </c>
+      <c r="M241" t="n">
+        <v>69.11631080838649</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -6008,6 +10102,24 @@
       <c r="G242" t="n">
         <v>896102270.0910474</v>
       </c>
+      <c r="H242" t="n">
+        <v>2659.3</v>
+      </c>
+      <c r="I242" t="n">
+        <v>2761.013519258741</v>
+      </c>
+      <c r="J242" t="n">
+        <v>2557.586480741259</v>
+      </c>
+      <c r="K242" t="n">
+        <v>22.969441951509</v>
+      </c>
+      <c r="L242" t="n">
+        <v>6.88472735390495</v>
+      </c>
+      <c r="M242" t="n">
+        <v>66.32981029730755</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -6031,6 +10143,24 @@
       <c r="G243" t="n">
         <v>961243761.0088856</v>
       </c>
+      <c r="H243" t="n">
+        <v>2662.05</v>
+      </c>
+      <c r="I243" t="n">
+        <v>2767.044237937128</v>
+      </c>
+      <c r="J243" t="n">
+        <v>2557.055762062872</v>
+      </c>
+      <c r="K243" t="n">
+        <v>22.95085113771665</v>
+      </c>
+      <c r="L243" t="n">
+        <v>10.09795211066729</v>
+      </c>
+      <c r="M243" t="n">
+        <v>57.67873832869003</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -6054,6 +10184,24 @@
       <c r="G244" t="n">
         <v>486105150.5670351</v>
       </c>
+      <c r="H244" t="n">
+        <v>2665.1</v>
+      </c>
+      <c r="I244" t="n">
+        <v>2771.126223171431</v>
+      </c>
+      <c r="J244" t="n">
+        <v>2559.073776828568</v>
+      </c>
+      <c r="K244" t="n">
+        <v>21.3983842478483</v>
+      </c>
+      <c r="L244" t="n">
+        <v>12.35803853810349</v>
+      </c>
+      <c r="M244" t="n">
+        <v>54.45808062574599</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -6077,6 +10225,24 @@
       <c r="G245" t="n">
         <v>361051032.9378421</v>
       </c>
+      <c r="H245" t="n">
+        <v>2668.15</v>
+      </c>
+      <c r="I245" t="n">
+        <v>2773.353184362443</v>
+      </c>
+      <c r="J245" t="n">
+        <v>2562.946815637557</v>
+      </c>
+      <c r="K245" t="n">
+        <v>18.90117076720708</v>
+      </c>
+      <c r="L245" t="n">
+        <v>13.66666498392421</v>
+      </c>
+      <c r="M245" t="n">
+        <v>51.92130269380812</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -6100,6 +10266,24 @@
       <c r="G246" t="n">
         <v>492576140.7818838</v>
       </c>
+      <c r="H246" t="n">
+        <v>2672.25</v>
+      </c>
+      <c r="I246" t="n">
+        <v>2778.816176622783</v>
+      </c>
+      <c r="J246" t="n">
+        <v>2565.683823377217</v>
+      </c>
+      <c r="K246" t="n">
+        <v>19.12242891465712</v>
+      </c>
+      <c r="L246" t="n">
+        <v>14.75781777007079</v>
+      </c>
+      <c r="M246" t="n">
+        <v>56.90971222875322</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -6123,6 +10307,24 @@
       <c r="G247" t="n">
         <v>226956148.7400636</v>
       </c>
+      <c r="H247" t="n">
+        <v>2677</v>
+      </c>
+      <c r="I247" t="n">
+        <v>2782.107563952354</v>
+      </c>
+      <c r="J247" t="n">
+        <v>2571.892436047646</v>
+      </c>
+      <c r="K247" t="n">
+        <v>18.59922741861692</v>
+      </c>
+      <c r="L247" t="n">
+        <v>15.52609969978002</v>
+      </c>
+      <c r="M247" t="n">
+        <v>55.66573610674372</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -6146,6 +10348,24 @@
       <c r="G248" t="n">
         <v>377994237.6690109</v>
       </c>
+      <c r="H248" t="n">
+        <v>2682.85</v>
+      </c>
+      <c r="I248" t="n">
+        <v>2787.86290396898</v>
+      </c>
+      <c r="J248" t="n">
+        <v>2577.83709603102</v>
+      </c>
+      <c r="K248" t="n">
+        <v>19.89188462350148</v>
+      </c>
+      <c r="L248" t="n">
+        <v>16.39925668452431</v>
+      </c>
+      <c r="M248" t="n">
+        <v>59.4810358524558</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -6169,6 +10389,24 @@
       <c r="G249" t="n">
         <v>271217513.5723787</v>
       </c>
+      <c r="H249" t="n">
+        <v>2689</v>
+      </c>
+      <c r="I249" t="n">
+        <v>2788.621282866656</v>
+      </c>
+      <c r="J249" t="n">
+        <v>2589.378717133344</v>
+      </c>
+      <c r="K249" t="n">
+        <v>19.64092505896951</v>
+      </c>
+      <c r="L249" t="n">
+        <v>17.04759035941336</v>
+      </c>
+      <c r="M249" t="n">
+        <v>56.63780346428386</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -6192,6 +10430,24 @@
       <c r="G250" t="n">
         <v>196188941.7558142</v>
       </c>
+      <c r="H250" t="n">
+        <v>2695.15</v>
+      </c>
+      <c r="I250" t="n">
+        <v>2786.373407083918</v>
+      </c>
+      <c r="J250" t="n">
+        <v>2603.926592916082</v>
+      </c>
+      <c r="K250" t="n">
+        <v>18.90138779263862</v>
+      </c>
+      <c r="L250" t="n">
+        <v>17.41834984605841</v>
+      </c>
+      <c r="M250" t="n">
+        <v>55.75468988749832</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -6215,6 +10471,24 @@
       <c r="G251" t="n">
         <v>212370956.9461589</v>
       </c>
+      <c r="H251" t="n">
+        <v>2701.25</v>
+      </c>
+      <c r="I251" t="n">
+        <v>2784.882230629095</v>
+      </c>
+      <c r="J251" t="n">
+        <v>2617.617769370905</v>
+      </c>
+      <c r="K251" t="n">
+        <v>18.98407070029816</v>
+      </c>
+      <c r="L251" t="n">
+        <v>17.73149401690636</v>
+      </c>
+      <c r="M251" t="n">
+        <v>57.70763272486951</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -6238,6 +10512,24 @@
       <c r="G252" t="n">
         <v>122069573.1701598</v>
       </c>
+      <c r="H252" t="n">
+        <v>2705</v>
+      </c>
+      <c r="I252" t="n">
+        <v>2786.336338742276</v>
+      </c>
+      <c r="J252" t="n">
+        <v>2623.663661257724</v>
+      </c>
+      <c r="K252" t="n">
+        <v>18.51341975102514</v>
+      </c>
+      <c r="L252" t="n">
+        <v>17.88787916373012</v>
+      </c>
+      <c r="M252" t="n">
+        <v>56.72709385816375</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -6261,6 +10553,24 @@
       <c r="G253" t="n">
         <v>211829669.0953471</v>
       </c>
+      <c r="H253" t="n">
+        <v>2709.6</v>
+      </c>
+      <c r="I253" t="n">
+        <v>2787.398200493316</v>
+      </c>
+      <c r="J253" t="n">
+        <v>2631.801799506684</v>
+      </c>
+      <c r="K253" t="n">
+        <v>18.73141778505851</v>
+      </c>
+      <c r="L253" t="n">
+        <v>18.0565868879958</v>
+      </c>
+      <c r="M253" t="n">
+        <v>58.62007357286777</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -6284,6 +10594,24 @@
       <c r="G254" t="n">
         <v>261372832.1496601</v>
       </c>
+      <c r="H254" t="n">
+        <v>2714.25</v>
+      </c>
+      <c r="I254" t="n">
+        <v>2782.243749712736</v>
+      </c>
+      <c r="J254" t="n">
+        <v>2646.256250287264</v>
+      </c>
+      <c r="K254" t="n">
+        <v>17.25285307913009</v>
+      </c>
+      <c r="L254" t="n">
+        <v>17.89584012622266</v>
+      </c>
+      <c r="M254" t="n">
+        <v>54.03776370759404</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -6307,6 +10635,24 @@
       <c r="G255" t="n">
         <v>254840867.6784808</v>
       </c>
+      <c r="H255" t="n">
+        <v>2719.7</v>
+      </c>
+      <c r="I255" t="n">
+        <v>2772.342568326386</v>
+      </c>
+      <c r="J255" t="n">
+        <v>2667.057431673614</v>
+      </c>
+      <c r="K255" t="n">
+        <v>16.61576844537831</v>
+      </c>
+      <c r="L255" t="n">
+        <v>17.63982579005379</v>
+      </c>
+      <c r="M255" t="n">
+        <v>55.8942346043716</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -6330,6 +10676,24 @@
       <c r="G256" t="n">
         <v>300733652.1602837</v>
       </c>
+      <c r="H256" t="n">
+        <v>2723.9</v>
+      </c>
+      <c r="I256" t="n">
+        <v>2763.502525171992</v>
+      </c>
+      <c r="J256" t="n">
+        <v>2684.297474828008</v>
+      </c>
+      <c r="K256" t="n">
+        <v>15.84750249648005</v>
+      </c>
+      <c r="L256" t="n">
+        <v>17.28136113133904</v>
+      </c>
+      <c r="M256" t="n">
+        <v>55.62538943795609</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -6353,6 +10717,24 @@
       <c r="G257" t="n">
         <v>53719748.10575927</v>
       </c>
+      <c r="H257" t="n">
+        <v>2726.35</v>
+      </c>
+      <c r="I257" t="n">
+        <v>2759.001339941849</v>
+      </c>
+      <c r="J257" t="n">
+        <v>2693.698660058151</v>
+      </c>
+      <c r="K257" t="n">
+        <v>14.74589809211284</v>
+      </c>
+      <c r="L257" t="n">
+        <v>16.7742685234938</v>
+      </c>
+      <c r="M257" t="n">
+        <v>54.49625271004194</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -6376,6 +10758,24 @@
       <c r="G258" t="n">
         <v>221586292.4018787</v>
       </c>
+      <c r="H258" t="n">
+        <v>2726.45</v>
+      </c>
+      <c r="I258" t="n">
+        <v>2759.169871637862</v>
+      </c>
+      <c r="J258" t="n">
+        <v>2693.730128362137</v>
+      </c>
+      <c r="K258" t="n">
+        <v>14.4327220135674</v>
+      </c>
+      <c r="L258" t="n">
+        <v>16.30595922150852</v>
+      </c>
+      <c r="M258" t="n">
+        <v>56.62947142986449</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -6399,6 +10799,24 @@
       <c r="G259" t="n">
         <v>116499274.95765</v>
       </c>
+      <c r="H259" t="n">
+        <v>2726.75</v>
+      </c>
+      <c r="I259" t="n">
+        <v>2759.152931966077</v>
+      </c>
+      <c r="J259" t="n">
+        <v>2694.347068033923</v>
+      </c>
+      <c r="K259" t="n">
+        <v>13.06561571825569</v>
+      </c>
+      <c r="L259" t="n">
+        <v>15.65789052085796</v>
+      </c>
+      <c r="M259" t="n">
+        <v>53.05788181639655</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -6422,6 +10840,24 @@
       <c r="G260" t="n">
         <v>180217356.0600389</v>
       </c>
+      <c r="H260" t="n">
+        <v>2725.25</v>
+      </c>
+      <c r="I260" t="n">
+        <v>2760.149140390534</v>
+      </c>
+      <c r="J260" t="n">
+        <v>2690.350859609466</v>
+      </c>
+      <c r="K260" t="n">
+        <v>9.931095222291333</v>
+      </c>
+      <c r="L260" t="n">
+        <v>14.51253146114463</v>
+      </c>
+      <c r="M260" t="n">
+        <v>46.71238328307037</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -6445,6 +10881,24 @@
       <c r="G261" t="n">
         <v>153699485.0058504</v>
       </c>
+      <c r="H261" t="n">
+        <v>2722.35</v>
+      </c>
+      <c r="I261" t="n">
+        <v>2751.766152025685</v>
+      </c>
+      <c r="J261" t="n">
+        <v>2692.933847974315</v>
+      </c>
+      <c r="K261" t="n">
+        <v>8.399136483603343</v>
+      </c>
+      <c r="L261" t="n">
+        <v>13.28985246563638</v>
+      </c>
+      <c r="M261" t="n">
+        <v>50.18751179695278</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -6468,6 +10922,24 @@
       <c r="G262" t="n">
         <v>135861669.9912941</v>
       </c>
+      <c r="H262" t="n">
+        <v>2719.45</v>
+      </c>
+      <c r="I262" t="n">
+        <v>2745.918660714101</v>
+      </c>
+      <c r="J262" t="n">
+        <v>2692.981339285899</v>
+      </c>
+      <c r="K262" t="n">
+        <v>6.225674377979885</v>
+      </c>
+      <c r="L262" t="n">
+        <v>11.87701684810508</v>
+      </c>
+      <c r="M262" t="n">
+        <v>47.37234903188435</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -6491,6 +10963,24 @@
       <c r="G263" t="n">
         <v>126686888.9660548</v>
       </c>
+      <c r="H263" t="n">
+        <v>2718.3</v>
+      </c>
+      <c r="I263" t="n">
+        <v>2746.676751047261</v>
+      </c>
+      <c r="J263" t="n">
+        <v>2689.923248952739</v>
+      </c>
+      <c r="K263" t="n">
+        <v>4.212555356446956</v>
+      </c>
+      <c r="L263" t="n">
+        <v>10.34412454977345</v>
+      </c>
+      <c r="M263" t="n">
+        <v>46.60454677087505</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -6514,6 +11004,24 @@
       <c r="G264" t="n">
         <v>169866449.2592375</v>
       </c>
+      <c r="H264" t="n">
+        <v>2718.45</v>
+      </c>
+      <c r="I264" t="n">
+        <v>2746.531844668722</v>
+      </c>
+      <c r="J264" t="n">
+        <v>2690.368155331278</v>
+      </c>
+      <c r="K264" t="n">
+        <v>3.38503982269367</v>
+      </c>
+      <c r="L264" t="n">
+        <v>8.952307604357499</v>
+      </c>
+      <c r="M264" t="n">
+        <v>49.54038312265954</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -6537,6 +11045,24 @@
       <c r="G265" t="n">
         <v>132912733.7805154</v>
       </c>
+      <c r="H265" t="n">
+        <v>2718.85</v>
+      </c>
+      <c r="I265" t="n">
+        <v>2745.490382880098</v>
+      </c>
+      <c r="J265" t="n">
+        <v>2692.209617119902</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2.05994885097607</v>
+      </c>
+      <c r="L265" t="n">
+        <v>7.573835853681214</v>
+      </c>
+      <c r="M265" t="n">
+        <v>47.29979763125164</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -6560,6 +11086,24 @@
       <c r="G266" t="n">
         <v>110433961.1805324</v>
       </c>
+      <c r="H266" t="n">
+        <v>2717.9</v>
+      </c>
+      <c r="I266" t="n">
+        <v>2745.640944468389</v>
+      </c>
+      <c r="J266" t="n">
+        <v>2690.159055531612</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1.237613202467855</v>
+      </c>
+      <c r="L266" t="n">
+        <v>6.306591323438543</v>
+      </c>
+      <c r="M266" t="n">
+        <v>48.24509751454681</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -6583,6 +11127,24 @@
       <c r="G267" t="n">
         <v>150180038.1006929</v>
       </c>
+      <c r="H267" t="n">
+        <v>2716.55</v>
+      </c>
+      <c r="I267" t="n">
+        <v>2747.375152067723</v>
+      </c>
+      <c r="J267" t="n">
+        <v>2685.724847932277</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-0.5375798349950855</v>
+      </c>
+      <c r="L267" t="n">
+        <v>4.937757091751817</v>
+      </c>
+      <c r="M267" t="n">
+        <v>44.25560994351731</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -6606,6 +11168,24 @@
       <c r="G268" t="n">
         <v>250958493.1203879</v>
       </c>
+      <c r="H268" t="n">
+        <v>2713.4</v>
+      </c>
+      <c r="I268" t="n">
+        <v>2747.513926774827</v>
+      </c>
+      <c r="J268" t="n">
+        <v>2679.286073225173</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-2.879539282181668</v>
+      </c>
+      <c r="L268" t="n">
+        <v>3.374297816965121</v>
+      </c>
+      <c r="M268" t="n">
+        <v>41.11709470372868</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -6629,6 +11209,24 @@
       <c r="G269" t="n">
         <v>194119273.2132617</v>
       </c>
+      <c r="H269" t="n">
+        <v>2710.4</v>
+      </c>
+      <c r="I269" t="n">
+        <v>2750.015148617647</v>
+      </c>
+      <c r="J269" t="n">
+        <v>2670.784851382353</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-5.479313330180503</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1.603575587535996</v>
+      </c>
+      <c r="M269" t="n">
+        <v>38.65681002832475</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -6652,6 +11250,24 @@
       <c r="G270" t="n">
         <v>119427798.198787</v>
       </c>
+      <c r="H270" t="n">
+        <v>2707.15</v>
+      </c>
+      <c r="I270" t="n">
+        <v>2752.937662093606</v>
+      </c>
+      <c r="J270" t="n">
+        <v>2661.362337906394</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-8.171679740091804</v>
+      </c>
+      <c r="L270" t="n">
+        <v>-0.3514754779895637</v>
+      </c>
+      <c r="M270" t="n">
+        <v>36.53780223079398</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -6675,6 +11291,24 @@
       <c r="G271" t="n">
         <v>157049026.2326372</v>
       </c>
+      <c r="H271" t="n">
+        <v>2702.95</v>
+      </c>
+      <c r="I271" t="n">
+        <v>2753.961665332532</v>
+      </c>
+      <c r="J271" t="n">
+        <v>2651.938334667468</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-10.82613570523563</v>
+      </c>
+      <c r="L271" t="n">
+        <v>-2.446407523438777</v>
+      </c>
+      <c r="M271" t="n">
+        <v>34.71613091425868</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -6698,6 +11332,24 @@
       <c r="G272" t="n">
         <v>226447651.7705278</v>
       </c>
+      <c r="H272" t="n">
+        <v>2699.3</v>
+      </c>
+      <c r="I272" t="n">
+        <v>2752.995809892377</v>
+      </c>
+      <c r="J272" t="n">
+        <v>2645.604190107623</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-12.22405834795154</v>
+      </c>
+      <c r="L272" t="n">
+        <v>-4.401937688341329</v>
+      </c>
+      <c r="M272" t="n">
+        <v>37.64559047170601</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -6721,6 +11373,24 @@
       <c r="G273" t="n">
         <v>207567616.2938294</v>
       </c>
+      <c r="H273" t="n">
+        <v>2695</v>
+      </c>
+      <c r="I273" t="n">
+        <v>2749.380143434882</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2640.619856565118</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-13.4193076167694</v>
+      </c>
+      <c r="L273" t="n">
+        <v>-6.205411674026944</v>
+      </c>
+      <c r="M273" t="n">
+        <v>36.88175280219234</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -6744,6 +11414,24 @@
       <c r="G274" t="n">
         <v>104658065.4906705</v>
       </c>
+      <c r="H274" t="n">
+        <v>2691.25</v>
+      </c>
+      <c r="I274" t="n">
+        <v>2748.485915297987</v>
+      </c>
+      <c r="J274" t="n">
+        <v>2634.014084702013</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-14.76123444998302</v>
+      </c>
+      <c r="L274" t="n">
+        <v>-7.91657622921816</v>
+      </c>
+      <c r="M274" t="n">
+        <v>35.09253516222938</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -6767,6 +11455,24 @@
       <c r="G275" t="n">
         <v>130020934.9046146</v>
       </c>
+      <c r="H275" t="n">
+        <v>2687.3</v>
+      </c>
+      <c r="I275" t="n">
+        <v>2744.473770209759</v>
+      </c>
+      <c r="J275" t="n">
+        <v>2630.126229790241</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-15.24552203213034</v>
+      </c>
+      <c r="L275" t="n">
+        <v>-9.382365389800597</v>
+      </c>
+      <c r="M275" t="n">
+        <v>37.42755923422495</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -6790,6 +11496,24 @@
       <c r="G276" t="n">
         <v>136802548.3260113</v>
       </c>
+      <c r="H276" t="n">
+        <v>2683.9</v>
+      </c>
+      <c r="I276" t="n">
+        <v>2739.039459554826</v>
+      </c>
+      <c r="J276" t="n">
+        <v>2628.760540445174</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-14.65349068444402</v>
+      </c>
+      <c r="L276" t="n">
+        <v>-10.43659044872928</v>
+      </c>
+      <c r="M276" t="n">
+        <v>41.92726075133086</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -6812,6 +11536,24 @@
       </c>
       <c r="G277" t="n">
         <v>199403461.8728677</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2679.35</v>
+      </c>
+      <c r="I277" t="n">
+        <v>2735.511463656126</v>
+      </c>
+      <c r="J277" t="n">
+        <v>2623.188536343874</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-16.17650326748799</v>
+      </c>
+      <c r="L277" t="n">
+        <v>-11.58457301248102</v>
+      </c>
+      <c r="M277" t="n">
+        <v>34.67648979389342</v>
       </c>
     </row>
   </sheetData>
